--- a/work-in-progress/Peppol Code Lists - Participant identifier schemes v9.6.xlsx
+++ b/work-in-progress/Peppol Code Lists - Participant identifier schemes v9.6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\git-peppol\peppol-edec-codelists\work-in-progress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4400EC-4637-4594-B62D-B466AE90774D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02217E6-5D3F-452A-B588-B7775AFB402A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29940" yWindow="1950" windowWidth="21495" windowHeight="18465" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25560" yWindow="255" windowWidth="25875" windowHeight="20160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Participant Identifier Scheme" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="634">
   <si>
     <t>Scheme ID</t>
   </si>
@@ -4729,7 +4729,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="17" spans="1:15 1028:1028" ht="120" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1028" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>493</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="18" spans="1:15 1028:1028" ht="120" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1028" ht="120" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>82</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="19" spans="1:15 1028:1028" ht="225" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1028" ht="225" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>87</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="20" spans="1:15 1028:1028" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1028" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>92</v>
       </c>
@@ -4881,42 +4881,1062 @@
         <v>528</v>
       </c>
     </row>
-    <row r="21" spans="1:15 1028:1028" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:1028" s="30" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="J21" s="6" t="s">
+      <c r="G21" s="27" t="s">
+        <v>483</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>628</v>
+      </c>
+      <c r="I21" s="31">
+        <v>46210</v>
+      </c>
+      <c r="J21" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K21" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="M21" s="7" t="s">
+      <c r="L21" s="27"/>
+      <c r="M21" s="27" t="s">
         <v>433</v>
       </c>
-      <c r="O21" s="7" t="s">
+      <c r="N21" s="25"/>
+      <c r="O21" s="27" t="s">
         <v>528</v>
       </c>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="25"/>
+      <c r="W21" s="25"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="25"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="25"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="25"/>
+      <c r="AH21" s="25"/>
+      <c r="AI21" s="25"/>
+      <c r="AJ21" s="25"/>
+      <c r="AK21" s="25"/>
+      <c r="AL21" s="25"/>
+      <c r="AM21" s="25"/>
+      <c r="AN21" s="25"/>
+      <c r="AO21" s="25"/>
+      <c r="AP21" s="25"/>
+      <c r="AQ21" s="25"/>
+      <c r="AR21" s="25"/>
+      <c r="AS21" s="25"/>
+      <c r="AT21" s="25"/>
+      <c r="AU21" s="25"/>
+      <c r="AV21" s="25"/>
+      <c r="AW21" s="25"/>
+      <c r="AX21" s="25"/>
+      <c r="AY21" s="25"/>
+      <c r="AZ21" s="25"/>
+      <c r="BA21" s="25"/>
+      <c r="BB21" s="25"/>
+      <c r="BC21" s="25"/>
+      <c r="BD21" s="25"/>
+      <c r="BE21" s="25"/>
+      <c r="BF21" s="25"/>
+      <c r="BG21" s="25"/>
+      <c r="BH21" s="25"/>
+      <c r="BI21" s="25"/>
+      <c r="BJ21" s="25"/>
+      <c r="BK21" s="25"/>
+      <c r="BL21" s="25"/>
+      <c r="BM21" s="25"/>
+      <c r="BN21" s="25"/>
+      <c r="BO21" s="25"/>
+      <c r="BP21" s="25"/>
+      <c r="BQ21" s="25"/>
+      <c r="BR21" s="25"/>
+      <c r="BS21" s="25"/>
+      <c r="BT21" s="25"/>
+      <c r="BU21" s="25"/>
+      <c r="BV21" s="25"/>
+      <c r="BW21" s="25"/>
+      <c r="BX21" s="25"/>
+      <c r="BY21" s="25"/>
+      <c r="BZ21" s="25"/>
+      <c r="CA21" s="25"/>
+      <c r="CB21" s="25"/>
+      <c r="CC21" s="25"/>
+      <c r="CD21" s="25"/>
+      <c r="CE21" s="25"/>
+      <c r="CF21" s="25"/>
+      <c r="CG21" s="25"/>
+      <c r="CH21" s="25"/>
+      <c r="CI21" s="25"/>
+      <c r="CJ21" s="25"/>
+      <c r="CK21" s="25"/>
+      <c r="CL21" s="25"/>
+      <c r="CM21" s="25"/>
+      <c r="CN21" s="25"/>
+      <c r="CO21" s="25"/>
+      <c r="CP21" s="25"/>
+      <c r="CQ21" s="25"/>
+      <c r="CR21" s="25"/>
+      <c r="CS21" s="25"/>
+      <c r="CT21" s="25"/>
+      <c r="CU21" s="25"/>
+      <c r="CV21" s="25"/>
+      <c r="CW21" s="25"/>
+      <c r="CX21" s="25"/>
+      <c r="CY21" s="25"/>
+      <c r="CZ21" s="25"/>
+      <c r="DA21" s="25"/>
+      <c r="DB21" s="25"/>
+      <c r="DC21" s="25"/>
+      <c r="DD21" s="25"/>
+      <c r="DE21" s="25"/>
+      <c r="DF21" s="25"/>
+      <c r="DG21" s="25"/>
+      <c r="DH21" s="25"/>
+      <c r="DI21" s="25"/>
+      <c r="DJ21" s="25"/>
+      <c r="DK21" s="25"/>
+      <c r="DL21" s="25"/>
+      <c r="DM21" s="25"/>
+      <c r="DN21" s="25"/>
+      <c r="DO21" s="25"/>
+      <c r="DP21" s="25"/>
+      <c r="DQ21" s="25"/>
+      <c r="DR21" s="25"/>
+      <c r="DS21" s="25"/>
+      <c r="DT21" s="25"/>
+      <c r="DU21" s="25"/>
+      <c r="DV21" s="25"/>
+      <c r="DW21" s="25"/>
+      <c r="DX21" s="25"/>
+      <c r="DY21" s="25"/>
+      <c r="DZ21" s="25"/>
+      <c r="EA21" s="25"/>
+      <c r="EB21" s="25"/>
+      <c r="EC21" s="25"/>
+      <c r="ED21" s="25"/>
+      <c r="EE21" s="25"/>
+      <c r="EF21" s="25"/>
+      <c r="EG21" s="25"/>
+      <c r="EH21" s="25"/>
+      <c r="EI21" s="25"/>
+      <c r="EJ21" s="25"/>
+      <c r="EK21" s="25"/>
+      <c r="EL21" s="25"/>
+      <c r="EM21" s="25"/>
+      <c r="EN21" s="25"/>
+      <c r="EO21" s="25"/>
+      <c r="EP21" s="25"/>
+      <c r="EQ21" s="25"/>
+      <c r="ER21" s="25"/>
+      <c r="ES21" s="25"/>
+      <c r="ET21" s="25"/>
+      <c r="EU21" s="25"/>
+      <c r="EV21" s="25"/>
+      <c r="EW21" s="25"/>
+      <c r="EX21" s="25"/>
+      <c r="EY21" s="25"/>
+      <c r="EZ21" s="25"/>
+      <c r="FA21" s="25"/>
+      <c r="FB21" s="25"/>
+      <c r="FC21" s="25"/>
+      <c r="FD21" s="25"/>
+      <c r="FE21" s="25"/>
+      <c r="FF21" s="25"/>
+      <c r="FG21" s="25"/>
+      <c r="FH21" s="25"/>
+      <c r="FI21" s="25"/>
+      <c r="FJ21" s="25"/>
+      <c r="FK21" s="25"/>
+      <c r="FL21" s="25"/>
+      <c r="FM21" s="25"/>
+      <c r="FN21" s="25"/>
+      <c r="FO21" s="25"/>
+      <c r="FP21" s="25"/>
+      <c r="FQ21" s="25"/>
+      <c r="FR21" s="25"/>
+      <c r="FS21" s="25"/>
+      <c r="FT21" s="25"/>
+      <c r="FU21" s="25"/>
+      <c r="FV21" s="25"/>
+      <c r="FW21" s="25"/>
+      <c r="FX21" s="25"/>
+      <c r="FY21" s="25"/>
+      <c r="FZ21" s="25"/>
+      <c r="GA21" s="25"/>
+      <c r="GB21" s="25"/>
+      <c r="GC21" s="25"/>
+      <c r="GD21" s="25"/>
+      <c r="GE21" s="25"/>
+      <c r="GF21" s="25"/>
+      <c r="GG21" s="25"/>
+      <c r="GH21" s="25"/>
+      <c r="GI21" s="25"/>
+      <c r="GJ21" s="25"/>
+      <c r="GK21" s="25"/>
+      <c r="GL21" s="25"/>
+      <c r="GM21" s="25"/>
+      <c r="GN21" s="25"/>
+      <c r="GO21" s="25"/>
+      <c r="GP21" s="25"/>
+      <c r="GQ21" s="25"/>
+      <c r="GR21" s="25"/>
+      <c r="GS21" s="25"/>
+      <c r="GT21" s="25"/>
+      <c r="GU21" s="25"/>
+      <c r="GV21" s="25"/>
+      <c r="GW21" s="25"/>
+      <c r="GX21" s="25"/>
+      <c r="GY21" s="25"/>
+      <c r="GZ21" s="25"/>
+      <c r="HA21" s="25"/>
+      <c r="HB21" s="25"/>
+      <c r="HC21" s="25"/>
+      <c r="HD21" s="25"/>
+      <c r="HE21" s="25"/>
+      <c r="HF21" s="25"/>
+      <c r="HG21" s="25"/>
+      <c r="HH21" s="25"/>
+      <c r="HI21" s="25"/>
+      <c r="HJ21" s="25"/>
+      <c r="HK21" s="25"/>
+      <c r="HL21" s="25"/>
+      <c r="HM21" s="25"/>
+      <c r="HN21" s="25"/>
+      <c r="HO21" s="25"/>
+      <c r="HP21" s="25"/>
+      <c r="HQ21" s="25"/>
+      <c r="HR21" s="25"/>
+      <c r="HS21" s="25"/>
+      <c r="HT21" s="25"/>
+      <c r="HU21" s="25"/>
+      <c r="HV21" s="25"/>
+      <c r="HW21" s="25"/>
+      <c r="HX21" s="25"/>
+      <c r="HY21" s="25"/>
+      <c r="HZ21" s="25"/>
+      <c r="IA21" s="25"/>
+      <c r="IB21" s="25"/>
+      <c r="IC21" s="25"/>
+      <c r="ID21" s="25"/>
+      <c r="IE21" s="25"/>
+      <c r="IF21" s="25"/>
+      <c r="IG21" s="25"/>
+      <c r="IH21" s="25"/>
+      <c r="II21" s="25"/>
+      <c r="IJ21" s="25"/>
+      <c r="IK21" s="25"/>
+      <c r="IL21" s="25"/>
+      <c r="IM21" s="25"/>
+      <c r="IN21" s="25"/>
+      <c r="IO21" s="25"/>
+      <c r="IP21" s="25"/>
+      <c r="IQ21" s="25"/>
+      <c r="IR21" s="25"/>
+      <c r="IS21" s="25"/>
+      <c r="IT21" s="25"/>
+      <c r="IU21" s="25"/>
+      <c r="IV21" s="25"/>
+      <c r="IW21" s="25"/>
+      <c r="IX21" s="25"/>
+      <c r="IY21" s="25"/>
+      <c r="IZ21" s="25"/>
+      <c r="JA21" s="25"/>
+      <c r="JB21" s="25"/>
+      <c r="JC21" s="25"/>
+      <c r="JD21" s="25"/>
+      <c r="JE21" s="25"/>
+      <c r="JF21" s="25"/>
+      <c r="JG21" s="25"/>
+      <c r="JH21" s="25"/>
+      <c r="JI21" s="25"/>
+      <c r="JJ21" s="25"/>
+      <c r="JK21" s="25"/>
+      <c r="JL21" s="25"/>
+      <c r="JM21" s="25"/>
+      <c r="JN21" s="25"/>
+      <c r="JO21" s="25"/>
+      <c r="JP21" s="25"/>
+      <c r="JQ21" s="25"/>
+      <c r="JR21" s="25"/>
+      <c r="JS21" s="25"/>
+      <c r="JT21" s="25"/>
+      <c r="JU21" s="25"/>
+      <c r="JV21" s="25"/>
+      <c r="JW21" s="25"/>
+      <c r="JX21" s="25"/>
+      <c r="JY21" s="25"/>
+      <c r="JZ21" s="25"/>
+      <c r="KA21" s="25"/>
+      <c r="KB21" s="25"/>
+      <c r="KC21" s="25"/>
+      <c r="KD21" s="25"/>
+      <c r="KE21" s="25"/>
+      <c r="KF21" s="25"/>
+      <c r="KG21" s="25"/>
+      <c r="KH21" s="25"/>
+      <c r="KI21" s="25"/>
+      <c r="KJ21" s="25"/>
+      <c r="KK21" s="25"/>
+      <c r="KL21" s="25"/>
+      <c r="KM21" s="25"/>
+      <c r="KN21" s="25"/>
+      <c r="KO21" s="25"/>
+      <c r="KP21" s="25"/>
+      <c r="KQ21" s="25"/>
+      <c r="KR21" s="25"/>
+      <c r="KS21" s="25"/>
+      <c r="KT21" s="25"/>
+      <c r="KU21" s="25"/>
+      <c r="KV21" s="25"/>
+      <c r="KW21" s="25"/>
+      <c r="KX21" s="25"/>
+      <c r="KY21" s="25"/>
+      <c r="KZ21" s="25"/>
+      <c r="LA21" s="25"/>
+      <c r="LB21" s="25"/>
+      <c r="LC21" s="25"/>
+      <c r="LD21" s="25"/>
+      <c r="LE21" s="25"/>
+      <c r="LF21" s="25"/>
+      <c r="LG21" s="25"/>
+      <c r="LH21" s="25"/>
+      <c r="LI21" s="25"/>
+      <c r="LJ21" s="25"/>
+      <c r="LK21" s="25"/>
+      <c r="LL21" s="25"/>
+      <c r="LM21" s="25"/>
+      <c r="LN21" s="25"/>
+      <c r="LO21" s="25"/>
+      <c r="LP21" s="25"/>
+      <c r="LQ21" s="25"/>
+      <c r="LR21" s="25"/>
+      <c r="LS21" s="25"/>
+      <c r="LT21" s="25"/>
+      <c r="LU21" s="25"/>
+      <c r="LV21" s="25"/>
+      <c r="LW21" s="25"/>
+      <c r="LX21" s="25"/>
+      <c r="LY21" s="25"/>
+      <c r="LZ21" s="25"/>
+      <c r="MA21" s="25"/>
+      <c r="MB21" s="25"/>
+      <c r="MC21" s="25"/>
+      <c r="MD21" s="25"/>
+      <c r="ME21" s="25"/>
+      <c r="MF21" s="25"/>
+      <c r="MG21" s="25"/>
+      <c r="MH21" s="25"/>
+      <c r="MI21" s="25"/>
+      <c r="MJ21" s="25"/>
+      <c r="MK21" s="25"/>
+      <c r="ML21" s="25"/>
+      <c r="MM21" s="25"/>
+      <c r="MN21" s="25"/>
+      <c r="MO21" s="25"/>
+      <c r="MP21" s="25"/>
+      <c r="MQ21" s="25"/>
+      <c r="MR21" s="25"/>
+      <c r="MS21" s="25"/>
+      <c r="MT21" s="25"/>
+      <c r="MU21" s="25"/>
+      <c r="MV21" s="25"/>
+      <c r="MW21" s="25"/>
+      <c r="MX21" s="25"/>
+      <c r="MY21" s="25"/>
+      <c r="MZ21" s="25"/>
+      <c r="NA21" s="25"/>
+      <c r="NB21" s="25"/>
+      <c r="NC21" s="25"/>
+      <c r="ND21" s="25"/>
+      <c r="NE21" s="25"/>
+      <c r="NF21" s="25"/>
+      <c r="NG21" s="25"/>
+      <c r="NH21" s="25"/>
+      <c r="NI21" s="25"/>
+      <c r="NJ21" s="25"/>
+      <c r="NK21" s="25"/>
+      <c r="NL21" s="25"/>
+      <c r="NM21" s="25"/>
+      <c r="NN21" s="25"/>
+      <c r="NO21" s="25"/>
+      <c r="NP21" s="25"/>
+      <c r="NQ21" s="25"/>
+      <c r="NR21" s="25"/>
+      <c r="NS21" s="25"/>
+      <c r="NT21" s="25"/>
+      <c r="NU21" s="25"/>
+      <c r="NV21" s="25"/>
+      <c r="NW21" s="25"/>
+      <c r="NX21" s="25"/>
+      <c r="NY21" s="25"/>
+      <c r="NZ21" s="25"/>
+      <c r="OA21" s="25"/>
+      <c r="OB21" s="25"/>
+      <c r="OC21" s="25"/>
+      <c r="OD21" s="25"/>
+      <c r="OE21" s="25"/>
+      <c r="OF21" s="25"/>
+      <c r="OG21" s="25"/>
+      <c r="OH21" s="25"/>
+      <c r="OI21" s="25"/>
+      <c r="OJ21" s="25"/>
+      <c r="OK21" s="25"/>
+      <c r="OL21" s="25"/>
+      <c r="OM21" s="25"/>
+      <c r="ON21" s="25"/>
+      <c r="OO21" s="25"/>
+      <c r="OP21" s="25"/>
+      <c r="OQ21" s="25"/>
+      <c r="OR21" s="25"/>
+      <c r="OS21" s="25"/>
+      <c r="OT21" s="25"/>
+      <c r="OU21" s="25"/>
+      <c r="OV21" s="25"/>
+      <c r="OW21" s="25"/>
+      <c r="OX21" s="25"/>
+      <c r="OY21" s="25"/>
+      <c r="OZ21" s="25"/>
+      <c r="PA21" s="25"/>
+      <c r="PB21" s="25"/>
+      <c r="PC21" s="25"/>
+      <c r="PD21" s="25"/>
+      <c r="PE21" s="25"/>
+      <c r="PF21" s="25"/>
+      <c r="PG21" s="25"/>
+      <c r="PH21" s="25"/>
+      <c r="PI21" s="25"/>
+      <c r="PJ21" s="25"/>
+      <c r="PK21" s="25"/>
+      <c r="PL21" s="25"/>
+      <c r="PM21" s="25"/>
+      <c r="PN21" s="25"/>
+      <c r="PO21" s="25"/>
+      <c r="PP21" s="25"/>
+      <c r="PQ21" s="25"/>
+      <c r="PR21" s="25"/>
+      <c r="PS21" s="25"/>
+      <c r="PT21" s="25"/>
+      <c r="PU21" s="25"/>
+      <c r="PV21" s="25"/>
+      <c r="PW21" s="25"/>
+      <c r="PX21" s="25"/>
+      <c r="PY21" s="25"/>
+      <c r="PZ21" s="25"/>
+      <c r="QA21" s="25"/>
+      <c r="QB21" s="25"/>
+      <c r="QC21" s="25"/>
+      <c r="QD21" s="25"/>
+      <c r="QE21" s="25"/>
+      <c r="QF21" s="25"/>
+      <c r="QG21" s="25"/>
+      <c r="QH21" s="25"/>
+      <c r="QI21" s="25"/>
+      <c r="QJ21" s="25"/>
+      <c r="QK21" s="25"/>
+      <c r="QL21" s="25"/>
+      <c r="QM21" s="25"/>
+      <c r="QN21" s="25"/>
+      <c r="QO21" s="25"/>
+      <c r="QP21" s="25"/>
+      <c r="QQ21" s="25"/>
+      <c r="QR21" s="25"/>
+      <c r="QS21" s="25"/>
+      <c r="QT21" s="25"/>
+      <c r="QU21" s="25"/>
+      <c r="QV21" s="25"/>
+      <c r="QW21" s="25"/>
+      <c r="QX21" s="25"/>
+      <c r="QY21" s="25"/>
+      <c r="QZ21" s="25"/>
+      <c r="RA21" s="25"/>
+      <c r="RB21" s="25"/>
+      <c r="RC21" s="25"/>
+      <c r="RD21" s="25"/>
+      <c r="RE21" s="25"/>
+      <c r="RF21" s="25"/>
+      <c r="RG21" s="25"/>
+      <c r="RH21" s="25"/>
+      <c r="RI21" s="25"/>
+      <c r="RJ21" s="25"/>
+      <c r="RK21" s="25"/>
+      <c r="RL21" s="25"/>
+      <c r="RM21" s="25"/>
+      <c r="RN21" s="25"/>
+      <c r="RO21" s="25"/>
+      <c r="RP21" s="25"/>
+      <c r="RQ21" s="25"/>
+      <c r="RR21" s="25"/>
+      <c r="RS21" s="25"/>
+      <c r="RT21" s="25"/>
+      <c r="RU21" s="25"/>
+      <c r="RV21" s="25"/>
+      <c r="RW21" s="25"/>
+      <c r="RX21" s="25"/>
+      <c r="RY21" s="25"/>
+      <c r="RZ21" s="25"/>
+      <c r="SA21" s="25"/>
+      <c r="SB21" s="25"/>
+      <c r="SC21" s="25"/>
+      <c r="SD21" s="25"/>
+      <c r="SE21" s="25"/>
+      <c r="SF21" s="25"/>
+      <c r="SG21" s="25"/>
+      <c r="SH21" s="25"/>
+      <c r="SI21" s="25"/>
+      <c r="SJ21" s="25"/>
+      <c r="SK21" s="25"/>
+      <c r="SL21" s="25"/>
+      <c r="SM21" s="25"/>
+      <c r="SN21" s="25"/>
+      <c r="SO21" s="25"/>
+      <c r="SP21" s="25"/>
+      <c r="SQ21" s="25"/>
+      <c r="SR21" s="25"/>
+      <c r="SS21" s="25"/>
+      <c r="ST21" s="25"/>
+      <c r="SU21" s="25"/>
+      <c r="SV21" s="25"/>
+      <c r="SW21" s="25"/>
+      <c r="SX21" s="25"/>
+      <c r="SY21" s="25"/>
+      <c r="SZ21" s="25"/>
+      <c r="TA21" s="25"/>
+      <c r="TB21" s="25"/>
+      <c r="TC21" s="25"/>
+      <c r="TD21" s="25"/>
+      <c r="TE21" s="25"/>
+      <c r="TF21" s="25"/>
+      <c r="TG21" s="25"/>
+      <c r="TH21" s="25"/>
+      <c r="TI21" s="25"/>
+      <c r="TJ21" s="25"/>
+      <c r="TK21" s="25"/>
+      <c r="TL21" s="25"/>
+      <c r="TM21" s="25"/>
+      <c r="TN21" s="25"/>
+      <c r="TO21" s="25"/>
+      <c r="TP21" s="25"/>
+      <c r="TQ21" s="25"/>
+      <c r="TR21" s="25"/>
+      <c r="TS21" s="25"/>
+      <c r="TT21" s="25"/>
+      <c r="TU21" s="25"/>
+      <c r="TV21" s="25"/>
+      <c r="TW21" s="25"/>
+      <c r="TX21" s="25"/>
+      <c r="TY21" s="25"/>
+      <c r="TZ21" s="25"/>
+      <c r="UA21" s="25"/>
+      <c r="UB21" s="25"/>
+      <c r="UC21" s="25"/>
+      <c r="UD21" s="25"/>
+      <c r="UE21" s="25"/>
+      <c r="UF21" s="25"/>
+      <c r="UG21" s="25"/>
+      <c r="UH21" s="25"/>
+      <c r="UI21" s="25"/>
+      <c r="UJ21" s="25"/>
+      <c r="UK21" s="25"/>
+      <c r="UL21" s="25"/>
+      <c r="UM21" s="25"/>
+      <c r="UN21" s="25"/>
+      <c r="UO21" s="25"/>
+      <c r="UP21" s="25"/>
+      <c r="UQ21" s="25"/>
+      <c r="UR21" s="25"/>
+      <c r="US21" s="25"/>
+      <c r="UT21" s="25"/>
+      <c r="UU21" s="25"/>
+      <c r="UV21" s="25"/>
+      <c r="UW21" s="25"/>
+      <c r="UX21" s="25"/>
+      <c r="UY21" s="25"/>
+      <c r="UZ21" s="25"/>
+      <c r="VA21" s="25"/>
+      <c r="VB21" s="25"/>
+      <c r="VC21" s="25"/>
+      <c r="VD21" s="25"/>
+      <c r="VE21" s="25"/>
+      <c r="VF21" s="25"/>
+      <c r="VG21" s="25"/>
+      <c r="VH21" s="25"/>
+      <c r="VI21" s="25"/>
+      <c r="VJ21" s="25"/>
+      <c r="VK21" s="25"/>
+      <c r="VL21" s="25"/>
+      <c r="VM21" s="25"/>
+      <c r="VN21" s="25"/>
+      <c r="VO21" s="25"/>
+      <c r="VP21" s="25"/>
+      <c r="VQ21" s="25"/>
+      <c r="VR21" s="25"/>
+      <c r="VS21" s="25"/>
+      <c r="VT21" s="25"/>
+      <c r="VU21" s="25"/>
+      <c r="VV21" s="25"/>
+      <c r="VW21" s="25"/>
+      <c r="VX21" s="25"/>
+      <c r="VY21" s="25"/>
+      <c r="VZ21" s="25"/>
+      <c r="WA21" s="25"/>
+      <c r="WB21" s="25"/>
+      <c r="WC21" s="25"/>
+      <c r="WD21" s="25"/>
+      <c r="WE21" s="25"/>
+      <c r="WF21" s="25"/>
+      <c r="WG21" s="25"/>
+      <c r="WH21" s="25"/>
+      <c r="WI21" s="25"/>
+      <c r="WJ21" s="25"/>
+      <c r="WK21" s="25"/>
+      <c r="WL21" s="25"/>
+      <c r="WM21" s="25"/>
+      <c r="WN21" s="25"/>
+      <c r="WO21" s="25"/>
+      <c r="WP21" s="25"/>
+      <c r="WQ21" s="25"/>
+      <c r="WR21" s="25"/>
+      <c r="WS21" s="25"/>
+      <c r="WT21" s="25"/>
+      <c r="WU21" s="25"/>
+      <c r="WV21" s="25"/>
+      <c r="WW21" s="25"/>
+      <c r="WX21" s="25"/>
+      <c r="WY21" s="25"/>
+      <c r="WZ21" s="25"/>
+      <c r="XA21" s="25"/>
+      <c r="XB21" s="25"/>
+      <c r="XC21" s="25"/>
+      <c r="XD21" s="25"/>
+      <c r="XE21" s="25"/>
+      <c r="XF21" s="25"/>
+      <c r="XG21" s="25"/>
+      <c r="XH21" s="25"/>
+      <c r="XI21" s="25"/>
+      <c r="XJ21" s="25"/>
+      <c r="XK21" s="25"/>
+      <c r="XL21" s="25"/>
+      <c r="XM21" s="25"/>
+      <c r="XN21" s="25"/>
+      <c r="XO21" s="25"/>
+      <c r="XP21" s="25"/>
+      <c r="XQ21" s="25"/>
+      <c r="XR21" s="25"/>
+      <c r="XS21" s="25"/>
+      <c r="XT21" s="25"/>
+      <c r="XU21" s="25"/>
+      <c r="XV21" s="25"/>
+      <c r="XW21" s="25"/>
+      <c r="XX21" s="25"/>
+      <c r="XY21" s="25"/>
+      <c r="XZ21" s="25"/>
+      <c r="YA21" s="25"/>
+      <c r="YB21" s="25"/>
+      <c r="YC21" s="25"/>
+      <c r="YD21" s="25"/>
+      <c r="YE21" s="25"/>
+      <c r="YF21" s="25"/>
+      <c r="YG21" s="25"/>
+      <c r="YH21" s="25"/>
+      <c r="YI21" s="25"/>
+      <c r="YJ21" s="25"/>
+      <c r="YK21" s="25"/>
+      <c r="YL21" s="25"/>
+      <c r="YM21" s="25"/>
+      <c r="YN21" s="25"/>
+      <c r="YO21" s="25"/>
+      <c r="YP21" s="25"/>
+      <c r="YQ21" s="25"/>
+      <c r="YR21" s="25"/>
+      <c r="YS21" s="25"/>
+      <c r="YT21" s="25"/>
+      <c r="YU21" s="25"/>
+      <c r="YV21" s="25"/>
+      <c r="YW21" s="25"/>
+      <c r="YX21" s="25"/>
+      <c r="YY21" s="25"/>
+      <c r="YZ21" s="25"/>
+      <c r="ZA21" s="25"/>
+      <c r="ZB21" s="25"/>
+      <c r="ZC21" s="25"/>
+      <c r="ZD21" s="25"/>
+      <c r="ZE21" s="25"/>
+      <c r="ZF21" s="25"/>
+      <c r="ZG21" s="25"/>
+      <c r="ZH21" s="25"/>
+      <c r="ZI21" s="25"/>
+      <c r="ZJ21" s="25"/>
+      <c r="ZK21" s="25"/>
+      <c r="ZL21" s="25"/>
+      <c r="ZM21" s="25"/>
+      <c r="ZN21" s="25"/>
+      <c r="ZO21" s="25"/>
+      <c r="ZP21" s="25"/>
+      <c r="ZQ21" s="25"/>
+      <c r="ZR21" s="25"/>
+      <c r="ZS21" s="25"/>
+      <c r="ZT21" s="25"/>
+      <c r="ZU21" s="25"/>
+      <c r="ZV21" s="25"/>
+      <c r="ZW21" s="25"/>
+      <c r="ZX21" s="25"/>
+      <c r="ZY21" s="25"/>
+      <c r="ZZ21" s="25"/>
+      <c r="AAA21" s="25"/>
+      <c r="AAB21" s="25"/>
+      <c r="AAC21" s="25"/>
+      <c r="AAD21" s="25"/>
+      <c r="AAE21" s="25"/>
+      <c r="AAF21" s="25"/>
+      <c r="AAG21" s="25"/>
+      <c r="AAH21" s="25"/>
+      <c r="AAI21" s="25"/>
+      <c r="AAJ21" s="25"/>
+      <c r="AAK21" s="25"/>
+      <c r="AAL21" s="25"/>
+      <c r="AAM21" s="25"/>
+      <c r="AAN21" s="25"/>
+      <c r="AAO21" s="25"/>
+      <c r="AAP21" s="25"/>
+      <c r="AAQ21" s="25"/>
+      <c r="AAR21" s="25"/>
+      <c r="AAS21" s="25"/>
+      <c r="AAT21" s="25"/>
+      <c r="AAU21" s="25"/>
+      <c r="AAV21" s="25"/>
+      <c r="AAW21" s="25"/>
+      <c r="AAX21" s="25"/>
+      <c r="AAY21" s="25"/>
+      <c r="AAZ21" s="25"/>
+      <c r="ABA21" s="25"/>
+      <c r="ABB21" s="25"/>
+      <c r="ABC21" s="25"/>
+      <c r="ABD21" s="25"/>
+      <c r="ABE21" s="25"/>
+      <c r="ABF21" s="25"/>
+      <c r="ABG21" s="25"/>
+      <c r="ABH21" s="25"/>
+      <c r="ABI21" s="25"/>
+      <c r="ABJ21" s="25"/>
+      <c r="ABK21" s="25"/>
+      <c r="ABL21" s="25"/>
+      <c r="ABM21" s="25"/>
+      <c r="ABN21" s="25"/>
+      <c r="ABO21" s="25"/>
+      <c r="ABP21" s="25"/>
+      <c r="ABQ21" s="25"/>
+      <c r="ABR21" s="25"/>
+      <c r="ABS21" s="25"/>
+      <c r="ABT21" s="25"/>
+      <c r="ABU21" s="25"/>
+      <c r="ABV21" s="25"/>
+      <c r="ABW21" s="25"/>
+      <c r="ABX21" s="25"/>
+      <c r="ABY21" s="25"/>
+      <c r="ABZ21" s="25"/>
+      <c r="ACA21" s="25"/>
+      <c r="ACB21" s="25"/>
+      <c r="ACC21" s="25"/>
+      <c r="ACD21" s="25"/>
+      <c r="ACE21" s="25"/>
+      <c r="ACF21" s="25"/>
+      <c r="ACG21" s="25"/>
+      <c r="ACH21" s="25"/>
+      <c r="ACI21" s="25"/>
+      <c r="ACJ21" s="25"/>
+      <c r="ACK21" s="25"/>
+      <c r="ACL21" s="25"/>
+      <c r="ACM21" s="25"/>
+      <c r="ACN21" s="25"/>
+      <c r="ACO21" s="25"/>
+      <c r="ACP21" s="25"/>
+      <c r="ACQ21" s="25"/>
+      <c r="ACR21" s="25"/>
+      <c r="ACS21" s="25"/>
+      <c r="ACT21" s="25"/>
+      <c r="ACU21" s="25"/>
+      <c r="ACV21" s="25"/>
+      <c r="ACW21" s="25"/>
+      <c r="ACX21" s="25"/>
+      <c r="ACY21" s="25"/>
+      <c r="ACZ21" s="25"/>
+      <c r="ADA21" s="25"/>
+      <c r="ADB21" s="25"/>
+      <c r="ADC21" s="25"/>
+      <c r="ADD21" s="25"/>
+      <c r="ADE21" s="25"/>
+      <c r="ADF21" s="25"/>
+      <c r="ADG21" s="25"/>
+      <c r="ADH21" s="25"/>
+      <c r="ADI21" s="25"/>
+      <c r="ADJ21" s="25"/>
+      <c r="ADK21" s="25"/>
+      <c r="ADL21" s="25"/>
+      <c r="ADM21" s="25"/>
+      <c r="ADN21" s="25"/>
+      <c r="ADO21" s="25"/>
+      <c r="ADP21" s="25"/>
+      <c r="ADQ21" s="25"/>
+      <c r="ADR21" s="25"/>
+      <c r="ADS21" s="25"/>
+      <c r="ADT21" s="25"/>
+      <c r="ADU21" s="25"/>
+      <c r="ADV21" s="25"/>
+      <c r="ADW21" s="25"/>
+      <c r="ADX21" s="25"/>
+      <c r="ADY21" s="25"/>
+      <c r="ADZ21" s="25"/>
+      <c r="AEA21" s="25"/>
+      <c r="AEB21" s="25"/>
+      <c r="AEC21" s="25"/>
+      <c r="AED21" s="25"/>
+      <c r="AEE21" s="25"/>
+      <c r="AEF21" s="25"/>
+      <c r="AEG21" s="25"/>
+      <c r="AEH21" s="25"/>
+      <c r="AEI21" s="25"/>
+      <c r="AEJ21" s="25"/>
+      <c r="AEK21" s="25"/>
+      <c r="AEL21" s="25"/>
+      <c r="AEM21" s="25"/>
+      <c r="AEN21" s="25"/>
+      <c r="AEO21" s="25"/>
+      <c r="AEP21" s="25"/>
+      <c r="AEQ21" s="25"/>
+      <c r="AER21" s="25"/>
+      <c r="AES21" s="25"/>
+      <c r="AET21" s="25"/>
+      <c r="AEU21" s="25"/>
+      <c r="AEV21" s="25"/>
+      <c r="AEW21" s="25"/>
+      <c r="AEX21" s="25"/>
+      <c r="AEY21" s="25"/>
+      <c r="AEZ21" s="25"/>
+      <c r="AFA21" s="25"/>
+      <c r="AFB21" s="25"/>
+      <c r="AFC21" s="25"/>
+      <c r="AFD21" s="25"/>
+      <c r="AFE21" s="25"/>
+      <c r="AFF21" s="25"/>
+      <c r="AFG21" s="25"/>
+      <c r="AFH21" s="25"/>
+      <c r="AFI21" s="25"/>
+      <c r="AFJ21" s="25"/>
+      <c r="AFK21" s="25"/>
+      <c r="AFL21" s="25"/>
+      <c r="AFM21" s="25"/>
+      <c r="AFN21" s="25"/>
+      <c r="AFO21" s="25"/>
+      <c r="AFP21" s="25"/>
+      <c r="AFQ21" s="25"/>
+      <c r="AFR21" s="25"/>
+      <c r="AFS21" s="25"/>
+      <c r="AFT21" s="25"/>
+      <c r="AFU21" s="25"/>
+      <c r="AFV21" s="25"/>
+      <c r="AFW21" s="25"/>
+      <c r="AFX21" s="25"/>
+      <c r="AFY21" s="25"/>
+      <c r="AFZ21" s="25"/>
+      <c r="AGA21" s="25"/>
+      <c r="AGB21" s="25"/>
+      <c r="AGC21" s="25"/>
+      <c r="AGD21" s="25"/>
+      <c r="AGE21" s="25"/>
+      <c r="AGF21" s="25"/>
+      <c r="AGG21" s="25"/>
+      <c r="AGH21" s="25"/>
+      <c r="AGI21" s="25"/>
+      <c r="AGJ21" s="25"/>
+      <c r="AGK21" s="25"/>
+      <c r="AGL21" s="25"/>
+      <c r="AGM21" s="25"/>
+      <c r="AGN21" s="25"/>
+      <c r="AGO21" s="25"/>
+      <c r="AGP21" s="25"/>
+      <c r="AGQ21" s="25"/>
+      <c r="AGR21" s="25"/>
+      <c r="AGS21" s="25"/>
+      <c r="AGT21" s="25"/>
+      <c r="AGU21" s="25"/>
+      <c r="AGV21" s="25"/>
+      <c r="AGW21" s="25"/>
+      <c r="AGX21" s="25"/>
+      <c r="AGY21" s="25"/>
+      <c r="AGZ21" s="25"/>
+      <c r="AHA21" s="25"/>
+      <c r="AHB21" s="25"/>
+      <c r="AHC21" s="25"/>
+      <c r="AHD21" s="25"/>
+      <c r="AHE21" s="25"/>
+      <c r="AHF21" s="25"/>
+      <c r="AHG21" s="25"/>
+      <c r="AHH21" s="25"/>
+      <c r="AHI21" s="25"/>
+      <c r="AHJ21" s="25"/>
+      <c r="AHK21" s="25"/>
+      <c r="AHL21" s="25"/>
+      <c r="AHM21" s="25"/>
+      <c r="AHN21" s="25"/>
+      <c r="AHO21" s="25"/>
+      <c r="AHP21" s="25"/>
+      <c r="AHQ21" s="25"/>
+      <c r="AHR21" s="25"/>
+      <c r="AHS21" s="25"/>
+      <c r="AHT21" s="25"/>
+      <c r="AHU21" s="25"/>
+      <c r="AHV21" s="25"/>
+      <c r="AHW21" s="25"/>
+      <c r="AHX21" s="25"/>
+      <c r="AHY21" s="25"/>
+      <c r="AHZ21" s="25"/>
+      <c r="AIA21" s="25"/>
+      <c r="AIB21" s="25"/>
+      <c r="AIC21" s="25"/>
+      <c r="AID21" s="25"/>
+      <c r="AIE21" s="25"/>
+      <c r="AIF21" s="25"/>
+      <c r="AIG21" s="25"/>
+      <c r="AIH21" s="25"/>
+      <c r="AII21" s="25"/>
+      <c r="AIJ21" s="25"/>
+      <c r="AIK21" s="25"/>
+      <c r="AIL21" s="25"/>
+      <c r="AIM21" s="25"/>
+      <c r="AIN21" s="25"/>
+      <c r="AIO21" s="25"/>
+      <c r="AIP21" s="25"/>
+      <c r="AIQ21" s="25"/>
+      <c r="AIR21" s="25"/>
+      <c r="AIS21" s="25"/>
+      <c r="AIT21" s="25"/>
+      <c r="AIU21" s="25"/>
+      <c r="AIV21" s="25"/>
+      <c r="AIW21" s="25"/>
+      <c r="AIX21" s="25"/>
+      <c r="AIY21" s="25"/>
+      <c r="AIZ21" s="25"/>
+      <c r="AJA21" s="25"/>
+      <c r="AJB21" s="25"/>
+      <c r="AJC21" s="25"/>
+      <c r="AJD21" s="25"/>
+      <c r="AJE21" s="25"/>
+      <c r="AJF21" s="25"/>
+      <c r="AJG21" s="25"/>
+      <c r="AJH21" s="25"/>
+      <c r="AJI21" s="25"/>
+      <c r="AJJ21" s="25"/>
+      <c r="AJK21" s="25"/>
+      <c r="AJL21" s="25"/>
+      <c r="AJM21" s="25"/>
+      <c r="AJN21" s="25"/>
+      <c r="AJO21" s="25"/>
+      <c r="AJP21" s="25"/>
+      <c r="AJQ21" s="25"/>
+      <c r="AJR21" s="25"/>
+      <c r="AJS21" s="25"/>
+      <c r="AJT21" s="25"/>
+      <c r="AJU21" s="25"/>
+      <c r="AJV21" s="25"/>
+      <c r="AJW21" s="25"/>
+      <c r="AJX21" s="25"/>
+      <c r="AJY21" s="25"/>
+      <c r="AJZ21" s="25"/>
+      <c r="AKA21" s="25"/>
+      <c r="AKB21" s="25"/>
+      <c r="AKC21" s="25"/>
+      <c r="AKD21" s="25"/>
+      <c r="AKE21" s="25"/>
+      <c r="AKF21" s="25"/>
+      <c r="AKG21" s="25"/>
+      <c r="AKH21" s="25"/>
+      <c r="AKI21" s="25"/>
+      <c r="AKJ21" s="25"/>
+      <c r="AKK21" s="25"/>
+      <c r="AKL21" s="25"/>
+      <c r="AKM21" s="25"/>
+      <c r="AKN21" s="25"/>
+      <c r="AKO21" s="25"/>
+      <c r="AKP21" s="25"/>
+      <c r="AKQ21" s="25"/>
+      <c r="AKR21" s="25"/>
+      <c r="AKS21" s="25"/>
+      <c r="AKT21" s="25"/>
+      <c r="AKU21" s="25"/>
+      <c r="AKV21" s="25"/>
+      <c r="AKW21" s="25"/>
+      <c r="AKX21" s="25"/>
+      <c r="AKY21" s="25"/>
+      <c r="AKZ21" s="25"/>
+      <c r="ALA21" s="25"/>
+      <c r="ALB21" s="25"/>
+      <c r="ALC21" s="25"/>
+      <c r="ALD21" s="25"/>
+      <c r="ALE21" s="25"/>
+      <c r="ALF21" s="25"/>
+      <c r="ALG21" s="25"/>
+      <c r="ALH21" s="25"/>
+      <c r="ALI21" s="25"/>
+      <c r="ALJ21" s="25"/>
+      <c r="ALK21" s="25"/>
+      <c r="ALL21" s="25"/>
+      <c r="ALM21" s="25"/>
+      <c r="ALN21" s="25"/>
+      <c r="ALO21" s="25"/>
+      <c r="ALP21" s="25"/>
+      <c r="ALQ21" s="25"/>
+      <c r="ALR21" s="25"/>
+      <c r="ALS21" s="25"/>
+      <c r="ALT21" s="25"/>
+      <c r="ALU21" s="25"/>
+      <c r="ALV21" s="25"/>
+      <c r="ALW21" s="25"/>
+      <c r="ALX21" s="25"/>
+      <c r="ALY21" s="25"/>
+      <c r="ALZ21" s="25"/>
+      <c r="AMA21" s="25"/>
+      <c r="AMB21" s="25"/>
+      <c r="AMC21" s="25"/>
+      <c r="AMD21" s="25"/>
+      <c r="AME21" s="25"/>
+      <c r="AMF21" s="25"/>
+      <c r="AMG21" s="25"/>
+      <c r="AMH21" s="25"/>
+      <c r="AMI21" s="25"/>
+      <c r="AMJ21" s="25"/>
+      <c r="AMK21" s="25"/>
+      <c r="AML21" s="25"/>
+      <c r="AMM21" s="25"/>
     </row>
-    <row r="22" spans="1:15 1028:1028" ht="105" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1028" ht="105" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>105</v>
       </c>
@@ -4954,7 +5974,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="23" spans="1:15 1028:1028" ht="90" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1028" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>110</v>
       </c>
@@ -4989,7 +6009,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="24" spans="1:15 1028:1028" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1028" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>341</v>
       </c>
@@ -5024,7 +6044,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="25" spans="1:15 1028:1028" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1028" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>349</v>
       </c>
@@ -5059,7 +6079,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="26" spans="1:15 1028:1028" ht="75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1028" ht="75" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>115</v>
       </c>
@@ -5097,7 +6117,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="27" spans="1:15 1028:1028" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1028" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>350</v>
       </c>
@@ -5137,7 +6157,7 @@
       </c>
       <c r="AMN27" s="4"/>
     </row>
-    <row r="28" spans="1:15 1028:1028" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1028" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>357</v>
       </c>
@@ -5177,7 +6197,7 @@
       </c>
       <c r="AMN28" s="4"/>
     </row>
-    <row r="29" spans="1:15 1028:1028" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1028" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>522</v>
       </c>
@@ -5212,7 +6232,7 @@
       </c>
       <c r="AMN29" s="4"/>
     </row>
-    <row r="30" spans="1:15 1028:1028" ht="105" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1028" ht="105" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>418</v>
       </c>
@@ -5249,7 +6269,7 @@
       </c>
       <c r="AMN30" s="4"/>
     </row>
-    <row r="31" spans="1:15 1028:1028" ht="75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1028" ht="75" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>453</v>
       </c>
@@ -5288,7 +6308,7 @@
       </c>
       <c r="AMN31" s="4"/>
     </row>
-    <row r="32" spans="1:15 1028:1028" ht="240" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1028" ht="240" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>479</v>
       </c>

--- a/work-in-progress/Peppol Code Lists - Participant identifier schemes v9.6.xlsx
+++ b/work-in-progress/Peppol Code Lists - Participant identifier schemes v9.6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\git-peppol\peppol-edec-codelists\work-in-progress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02217E6-5D3F-452A-B588-B7775AFB402A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD9742D-9F42-4682-B8C7-6135057DA094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25560" yWindow="255" windowWidth="25875" windowHeight="20160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="135" yWindow="720" windowWidth="25875" windowHeight="20160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Participant Identifier Scheme" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="635">
   <si>
     <t>Scheme ID</t>
   </si>
@@ -2242,6 +2242,9 @@
   </si>
   <si>
     <t>All organizations that are registered for VAT in Oman are obligated to issue and/or receive invoice electronically in the Sultanate of Oman and shall use the VATIN allocated by the Oman Tax Authority to uniquely identify themselves.</t>
+  </si>
+  <si>
+    <t>Use 0208 instead</t>
   </si>
 </sst>
 </file>
@@ -2347,7 +2350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2423,9 +2426,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4881,7 +4881,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="21" spans="1:1028" s="30" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1028" s="29" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>98</v>
       </c>
@@ -4906,20 +4906,22 @@
       <c r="H21" s="26" t="s">
         <v>628</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="30">
         <v>46210</v>
       </c>
-      <c r="J21" s="29" t="s">
+      <c r="J21" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="K21" s="29" t="s">
+      <c r="K21" s="28" t="s">
         <v>32</v>
       </c>
       <c r="L21" s="27"/>
       <c r="M21" s="27" t="s">
         <v>433</v>
       </c>
-      <c r="N21" s="25"/>
+      <c r="N21" s="25" t="s">
+        <v>634</v>
+      </c>
       <c r="O21" s="27" t="s">
         <v>528</v>
       </c>
@@ -17390,7 +17392,7 @@
       <c r="AML55" s="12"/>
       <c r="AMM55" s="12"/>
     </row>
-    <row r="56" spans="1:1027" s="30" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1027" s="29" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="25" t="s">
         <v>145</v>
       </c>
@@ -17415,9 +17417,9 @@
       <c r="H56" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="I56" s="31"/>
-      <c r="J56" s="29"/>
-      <c r="K56" s="29"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="28"/>
+      <c r="K56" s="28"/>
       <c r="L56" s="27" t="s">
         <v>152</v>
       </c>
@@ -18469,7 +18471,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="58" spans="1:1027" s="30" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1027" s="29" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A58" s="25" t="s">
         <v>153</v>
       </c>
@@ -18491,11 +18493,11 @@
       <c r="H58" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="I58" s="31"/>
-      <c r="J58" s="29" t="s">
+      <c r="I58" s="30"/>
+      <c r="J58" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="K58" s="29"/>
+      <c r="K58" s="28"/>
       <c r="L58" s="27"/>
       <c r="M58" s="27" t="s">
         <v>446</v>
@@ -19607,7 +19609,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="62" spans="1:1027" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1027" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="25" t="s">
         <v>169</v>
       </c>
@@ -19630,9 +19632,9 @@
       <c r="H62" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="I62" s="31"/>
-      <c r="J62" s="29"/>
-      <c r="K62" s="29"/>
+      <c r="I62" s="30"/>
+      <c r="J62" s="28"/>
+      <c r="K62" s="28"/>
       <c r="L62" s="27"/>
       <c r="M62" s="27"/>
       <c r="N62" s="25"/>
@@ -20652,7 +20654,7 @@
       <c r="AML62" s="25"/>
       <c r="AMM62" s="25"/>
     </row>
-    <row r="63" spans="1:1027" s="30" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1027" s="29" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A63" s="25" t="s">
         <v>174</v>
       </c>
@@ -20675,11 +20677,11 @@
       <c r="H63" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="I63" s="31"/>
-      <c r="J63" s="29" t="s">
+      <c r="I63" s="30"/>
+      <c r="J63" s="28" t="s">
         <v>372</v>
       </c>
-      <c r="K63" s="29" t="s">
+      <c r="K63" s="28" t="s">
         <v>379</v>
       </c>
       <c r="L63" s="27"/>
@@ -23611,1054 +23613,1054 @@
         <v>528</v>
       </c>
     </row>
-    <row r="100" spans="1:1027" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="25" t="s">
+    <row r="100" spans="1:1027" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="B100" s="25" t="s">
+      <c r="B100" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="C100" s="25" t="s">
+      <c r="C100" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D100" s="25" t="s">
+      <c r="D100" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="E100" s="25"/>
-      <c r="F100" s="26" t="s">
+      <c r="E100" s="12"/>
+      <c r="F100" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="G100" s="27" t="s">
-        <v>483</v>
-      </c>
-      <c r="H100" s="26" t="s">
+      <c r="G100" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="H100" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="I100" s="28">
+      <c r="I100" s="24">
         <v>46112</v>
       </c>
-      <c r="J100" s="29"/>
-      <c r="K100" s="29"/>
-      <c r="L100" s="27"/>
-      <c r="M100" s="27"/>
-      <c r="N100" s="25" t="s">
+      <c r="J100" s="15"/>
+      <c r="K100" s="15"/>
+      <c r="L100" s="14"/>
+      <c r="M100" s="14"/>
+      <c r="N100" s="12" t="s">
         <v>596</v>
       </c>
-      <c r="O100" s="27" t="s">
+      <c r="O100" s="14" t="s">
         <v>529</v>
       </c>
-      <c r="P100" s="25"/>
-      <c r="Q100" s="25"/>
-      <c r="R100" s="25"/>
-      <c r="S100" s="25"/>
-      <c r="T100" s="25"/>
-      <c r="U100" s="25"/>
-      <c r="V100" s="25"/>
-      <c r="W100" s="25"/>
-      <c r="X100" s="25"/>
-      <c r="Y100" s="25"/>
-      <c r="Z100" s="25"/>
-      <c r="AA100" s="25"/>
-      <c r="AB100" s="25"/>
-      <c r="AC100" s="25"/>
-      <c r="AD100" s="25"/>
-      <c r="AE100" s="25"/>
-      <c r="AF100" s="25"/>
-      <c r="AG100" s="25"/>
-      <c r="AH100" s="25"/>
-      <c r="AI100" s="25"/>
-      <c r="AJ100" s="25"/>
-      <c r="AK100" s="25"/>
-      <c r="AL100" s="25"/>
-      <c r="AM100" s="25"/>
-      <c r="AN100" s="25"/>
-      <c r="AO100" s="25"/>
-      <c r="AP100" s="25"/>
-      <c r="AQ100" s="25"/>
-      <c r="AR100" s="25"/>
-      <c r="AS100" s="25"/>
-      <c r="AT100" s="25"/>
-      <c r="AU100" s="25"/>
-      <c r="AV100" s="25"/>
-      <c r="AW100" s="25"/>
-      <c r="AX100" s="25"/>
-      <c r="AY100" s="25"/>
-      <c r="AZ100" s="25"/>
-      <c r="BA100" s="25"/>
-      <c r="BB100" s="25"/>
-      <c r="BC100" s="25"/>
-      <c r="BD100" s="25"/>
-      <c r="BE100" s="25"/>
-      <c r="BF100" s="25"/>
-      <c r="BG100" s="25"/>
-      <c r="BH100" s="25"/>
-      <c r="BI100" s="25"/>
-      <c r="BJ100" s="25"/>
-      <c r="BK100" s="25"/>
-      <c r="BL100" s="25"/>
-      <c r="BM100" s="25"/>
-      <c r="BN100" s="25"/>
-      <c r="BO100" s="25"/>
-      <c r="BP100" s="25"/>
-      <c r="BQ100" s="25"/>
-      <c r="BR100" s="25"/>
-      <c r="BS100" s="25"/>
-      <c r="BT100" s="25"/>
-      <c r="BU100" s="25"/>
-      <c r="BV100" s="25"/>
-      <c r="BW100" s="25"/>
-      <c r="BX100" s="25"/>
-      <c r="BY100" s="25"/>
-      <c r="BZ100" s="25"/>
-      <c r="CA100" s="25"/>
-      <c r="CB100" s="25"/>
-      <c r="CC100" s="25"/>
-      <c r="CD100" s="25"/>
-      <c r="CE100" s="25"/>
-      <c r="CF100" s="25"/>
-      <c r="CG100" s="25"/>
-      <c r="CH100" s="25"/>
-      <c r="CI100" s="25"/>
-      <c r="CJ100" s="25"/>
-      <c r="CK100" s="25"/>
-      <c r="CL100" s="25"/>
-      <c r="CM100" s="25"/>
-      <c r="CN100" s="25"/>
-      <c r="CO100" s="25"/>
-      <c r="CP100" s="25"/>
-      <c r="CQ100" s="25"/>
-      <c r="CR100" s="25"/>
-      <c r="CS100" s="25"/>
-      <c r="CT100" s="25"/>
-      <c r="CU100" s="25"/>
-      <c r="CV100" s="25"/>
-      <c r="CW100" s="25"/>
-      <c r="CX100" s="25"/>
-      <c r="CY100" s="25"/>
-      <c r="CZ100" s="25"/>
-      <c r="DA100" s="25"/>
-      <c r="DB100" s="25"/>
-      <c r="DC100" s="25"/>
-      <c r="DD100" s="25"/>
-      <c r="DE100" s="25"/>
-      <c r="DF100" s="25"/>
-      <c r="DG100" s="25"/>
-      <c r="DH100" s="25"/>
-      <c r="DI100" s="25"/>
-      <c r="DJ100" s="25"/>
-      <c r="DK100" s="25"/>
-      <c r="DL100" s="25"/>
-      <c r="DM100" s="25"/>
-      <c r="DN100" s="25"/>
-      <c r="DO100" s="25"/>
-      <c r="DP100" s="25"/>
-      <c r="DQ100" s="25"/>
-      <c r="DR100" s="25"/>
-      <c r="DS100" s="25"/>
-      <c r="DT100" s="25"/>
-      <c r="DU100" s="25"/>
-      <c r="DV100" s="25"/>
-      <c r="DW100" s="25"/>
-      <c r="DX100" s="25"/>
-      <c r="DY100" s="25"/>
-      <c r="DZ100" s="25"/>
-      <c r="EA100" s="25"/>
-      <c r="EB100" s="25"/>
-      <c r="EC100" s="25"/>
-      <c r="ED100" s="25"/>
-      <c r="EE100" s="25"/>
-      <c r="EF100" s="25"/>
-      <c r="EG100" s="25"/>
-      <c r="EH100" s="25"/>
-      <c r="EI100" s="25"/>
-      <c r="EJ100" s="25"/>
-      <c r="EK100" s="25"/>
-      <c r="EL100" s="25"/>
-      <c r="EM100" s="25"/>
-      <c r="EN100" s="25"/>
-      <c r="EO100" s="25"/>
-      <c r="EP100" s="25"/>
-      <c r="EQ100" s="25"/>
-      <c r="ER100" s="25"/>
-      <c r="ES100" s="25"/>
-      <c r="ET100" s="25"/>
-      <c r="EU100" s="25"/>
-      <c r="EV100" s="25"/>
-      <c r="EW100" s="25"/>
-      <c r="EX100" s="25"/>
-      <c r="EY100" s="25"/>
-      <c r="EZ100" s="25"/>
-      <c r="FA100" s="25"/>
-      <c r="FB100" s="25"/>
-      <c r="FC100" s="25"/>
-      <c r="FD100" s="25"/>
-      <c r="FE100" s="25"/>
-      <c r="FF100" s="25"/>
-      <c r="FG100" s="25"/>
-      <c r="FH100" s="25"/>
-      <c r="FI100" s="25"/>
-      <c r="FJ100" s="25"/>
-      <c r="FK100" s="25"/>
-      <c r="FL100" s="25"/>
-      <c r="FM100" s="25"/>
-      <c r="FN100" s="25"/>
-      <c r="FO100" s="25"/>
-      <c r="FP100" s="25"/>
-      <c r="FQ100" s="25"/>
-      <c r="FR100" s="25"/>
-      <c r="FS100" s="25"/>
-      <c r="FT100" s="25"/>
-      <c r="FU100" s="25"/>
-      <c r="FV100" s="25"/>
-      <c r="FW100" s="25"/>
-      <c r="FX100" s="25"/>
-      <c r="FY100" s="25"/>
-      <c r="FZ100" s="25"/>
-      <c r="GA100" s="25"/>
-      <c r="GB100" s="25"/>
-      <c r="GC100" s="25"/>
-      <c r="GD100" s="25"/>
-      <c r="GE100" s="25"/>
-      <c r="GF100" s="25"/>
-      <c r="GG100" s="25"/>
-      <c r="GH100" s="25"/>
-      <c r="GI100" s="25"/>
-      <c r="GJ100" s="25"/>
-      <c r="GK100" s="25"/>
-      <c r="GL100" s="25"/>
-      <c r="GM100" s="25"/>
-      <c r="GN100" s="25"/>
-      <c r="GO100" s="25"/>
-      <c r="GP100" s="25"/>
-      <c r="GQ100" s="25"/>
-      <c r="GR100" s="25"/>
-      <c r="GS100" s="25"/>
-      <c r="GT100" s="25"/>
-      <c r="GU100" s="25"/>
-      <c r="GV100" s="25"/>
-      <c r="GW100" s="25"/>
-      <c r="GX100" s="25"/>
-      <c r="GY100" s="25"/>
-      <c r="GZ100" s="25"/>
-      <c r="HA100" s="25"/>
-      <c r="HB100" s="25"/>
-      <c r="HC100" s="25"/>
-      <c r="HD100" s="25"/>
-      <c r="HE100" s="25"/>
-      <c r="HF100" s="25"/>
-      <c r="HG100" s="25"/>
-      <c r="HH100" s="25"/>
-      <c r="HI100" s="25"/>
-      <c r="HJ100" s="25"/>
-      <c r="HK100" s="25"/>
-      <c r="HL100" s="25"/>
-      <c r="HM100" s="25"/>
-      <c r="HN100" s="25"/>
-      <c r="HO100" s="25"/>
-      <c r="HP100" s="25"/>
-      <c r="HQ100" s="25"/>
-      <c r="HR100" s="25"/>
-      <c r="HS100" s="25"/>
-      <c r="HT100" s="25"/>
-      <c r="HU100" s="25"/>
-      <c r="HV100" s="25"/>
-      <c r="HW100" s="25"/>
-      <c r="HX100" s="25"/>
-      <c r="HY100" s="25"/>
-      <c r="HZ100" s="25"/>
-      <c r="IA100" s="25"/>
-      <c r="IB100" s="25"/>
-      <c r="IC100" s="25"/>
-      <c r="ID100" s="25"/>
-      <c r="IE100" s="25"/>
-      <c r="IF100" s="25"/>
-      <c r="IG100" s="25"/>
-      <c r="IH100" s="25"/>
-      <c r="II100" s="25"/>
-      <c r="IJ100" s="25"/>
-      <c r="IK100" s="25"/>
-      <c r="IL100" s="25"/>
-      <c r="IM100" s="25"/>
-      <c r="IN100" s="25"/>
-      <c r="IO100" s="25"/>
-      <c r="IP100" s="25"/>
-      <c r="IQ100" s="25"/>
-      <c r="IR100" s="25"/>
-      <c r="IS100" s="25"/>
-      <c r="IT100" s="25"/>
-      <c r="IU100" s="25"/>
-      <c r="IV100" s="25"/>
-      <c r="IW100" s="25"/>
-      <c r="IX100" s="25"/>
-      <c r="IY100" s="25"/>
-      <c r="IZ100" s="25"/>
-      <c r="JA100" s="25"/>
-      <c r="JB100" s="25"/>
-      <c r="JC100" s="25"/>
-      <c r="JD100" s="25"/>
-      <c r="JE100" s="25"/>
-      <c r="JF100" s="25"/>
-      <c r="JG100" s="25"/>
-      <c r="JH100" s="25"/>
-      <c r="JI100" s="25"/>
-      <c r="JJ100" s="25"/>
-      <c r="JK100" s="25"/>
-      <c r="JL100" s="25"/>
-      <c r="JM100" s="25"/>
-      <c r="JN100" s="25"/>
-      <c r="JO100" s="25"/>
-      <c r="JP100" s="25"/>
-      <c r="JQ100" s="25"/>
-      <c r="JR100" s="25"/>
-      <c r="JS100" s="25"/>
-      <c r="JT100" s="25"/>
-      <c r="JU100" s="25"/>
-      <c r="JV100" s="25"/>
-      <c r="JW100" s="25"/>
-      <c r="JX100" s="25"/>
-      <c r="JY100" s="25"/>
-      <c r="JZ100" s="25"/>
-      <c r="KA100" s="25"/>
-      <c r="KB100" s="25"/>
-      <c r="KC100" s="25"/>
-      <c r="KD100" s="25"/>
-      <c r="KE100" s="25"/>
-      <c r="KF100" s="25"/>
-      <c r="KG100" s="25"/>
-      <c r="KH100" s="25"/>
-      <c r="KI100" s="25"/>
-      <c r="KJ100" s="25"/>
-      <c r="KK100" s="25"/>
-      <c r="KL100" s="25"/>
-      <c r="KM100" s="25"/>
-      <c r="KN100" s="25"/>
-      <c r="KO100" s="25"/>
-      <c r="KP100" s="25"/>
-      <c r="KQ100" s="25"/>
-      <c r="KR100" s="25"/>
-      <c r="KS100" s="25"/>
-      <c r="KT100" s="25"/>
-      <c r="KU100" s="25"/>
-      <c r="KV100" s="25"/>
-      <c r="KW100" s="25"/>
-      <c r="KX100" s="25"/>
-      <c r="KY100" s="25"/>
-      <c r="KZ100" s="25"/>
-      <c r="LA100" s="25"/>
-      <c r="LB100" s="25"/>
-      <c r="LC100" s="25"/>
-      <c r="LD100" s="25"/>
-      <c r="LE100" s="25"/>
-      <c r="LF100" s="25"/>
-      <c r="LG100" s="25"/>
-      <c r="LH100" s="25"/>
-      <c r="LI100" s="25"/>
-      <c r="LJ100" s="25"/>
-      <c r="LK100" s="25"/>
-      <c r="LL100" s="25"/>
-      <c r="LM100" s="25"/>
-      <c r="LN100" s="25"/>
-      <c r="LO100" s="25"/>
-      <c r="LP100" s="25"/>
-      <c r="LQ100" s="25"/>
-      <c r="LR100" s="25"/>
-      <c r="LS100" s="25"/>
-      <c r="LT100" s="25"/>
-      <c r="LU100" s="25"/>
-      <c r="LV100" s="25"/>
-      <c r="LW100" s="25"/>
-      <c r="LX100" s="25"/>
-      <c r="LY100" s="25"/>
-      <c r="LZ100" s="25"/>
-      <c r="MA100" s="25"/>
-      <c r="MB100" s="25"/>
-      <c r="MC100" s="25"/>
-      <c r="MD100" s="25"/>
-      <c r="ME100" s="25"/>
-      <c r="MF100" s="25"/>
-      <c r="MG100" s="25"/>
-      <c r="MH100" s="25"/>
-      <c r="MI100" s="25"/>
-      <c r="MJ100" s="25"/>
-      <c r="MK100" s="25"/>
-      <c r="ML100" s="25"/>
-      <c r="MM100" s="25"/>
-      <c r="MN100" s="25"/>
-      <c r="MO100" s="25"/>
-      <c r="MP100" s="25"/>
-      <c r="MQ100" s="25"/>
-      <c r="MR100" s="25"/>
-      <c r="MS100" s="25"/>
-      <c r="MT100" s="25"/>
-      <c r="MU100" s="25"/>
-      <c r="MV100" s="25"/>
-      <c r="MW100" s="25"/>
-      <c r="MX100" s="25"/>
-      <c r="MY100" s="25"/>
-      <c r="MZ100" s="25"/>
-      <c r="NA100" s="25"/>
-      <c r="NB100" s="25"/>
-      <c r="NC100" s="25"/>
-      <c r="ND100" s="25"/>
-      <c r="NE100" s="25"/>
-      <c r="NF100" s="25"/>
-      <c r="NG100" s="25"/>
-      <c r="NH100" s="25"/>
-      <c r="NI100" s="25"/>
-      <c r="NJ100" s="25"/>
-      <c r="NK100" s="25"/>
-      <c r="NL100" s="25"/>
-      <c r="NM100" s="25"/>
-      <c r="NN100" s="25"/>
-      <c r="NO100" s="25"/>
-      <c r="NP100" s="25"/>
-      <c r="NQ100" s="25"/>
-      <c r="NR100" s="25"/>
-      <c r="NS100" s="25"/>
-      <c r="NT100" s="25"/>
-      <c r="NU100" s="25"/>
-      <c r="NV100" s="25"/>
-      <c r="NW100" s="25"/>
-      <c r="NX100" s="25"/>
-      <c r="NY100" s="25"/>
-      <c r="NZ100" s="25"/>
-      <c r="OA100" s="25"/>
-      <c r="OB100" s="25"/>
-      <c r="OC100" s="25"/>
-      <c r="OD100" s="25"/>
-      <c r="OE100" s="25"/>
-      <c r="OF100" s="25"/>
-      <c r="OG100" s="25"/>
-      <c r="OH100" s="25"/>
-      <c r="OI100" s="25"/>
-      <c r="OJ100" s="25"/>
-      <c r="OK100" s="25"/>
-      <c r="OL100" s="25"/>
-      <c r="OM100" s="25"/>
-      <c r="ON100" s="25"/>
-      <c r="OO100" s="25"/>
-      <c r="OP100" s="25"/>
-      <c r="OQ100" s="25"/>
-      <c r="OR100" s="25"/>
-      <c r="OS100" s="25"/>
-      <c r="OT100" s="25"/>
-      <c r="OU100" s="25"/>
-      <c r="OV100" s="25"/>
-      <c r="OW100" s="25"/>
-      <c r="OX100" s="25"/>
-      <c r="OY100" s="25"/>
-      <c r="OZ100" s="25"/>
-      <c r="PA100" s="25"/>
-      <c r="PB100" s="25"/>
-      <c r="PC100" s="25"/>
-      <c r="PD100" s="25"/>
-      <c r="PE100" s="25"/>
-      <c r="PF100" s="25"/>
-      <c r="PG100" s="25"/>
-      <c r="PH100" s="25"/>
-      <c r="PI100" s="25"/>
-      <c r="PJ100" s="25"/>
-      <c r="PK100" s="25"/>
-      <c r="PL100" s="25"/>
-      <c r="PM100" s="25"/>
-      <c r="PN100" s="25"/>
-      <c r="PO100" s="25"/>
-      <c r="PP100" s="25"/>
-      <c r="PQ100" s="25"/>
-      <c r="PR100" s="25"/>
-      <c r="PS100" s="25"/>
-      <c r="PT100" s="25"/>
-      <c r="PU100" s="25"/>
-      <c r="PV100" s="25"/>
-      <c r="PW100" s="25"/>
-      <c r="PX100" s="25"/>
-      <c r="PY100" s="25"/>
-      <c r="PZ100" s="25"/>
-      <c r="QA100" s="25"/>
-      <c r="QB100" s="25"/>
-      <c r="QC100" s="25"/>
-      <c r="QD100" s="25"/>
-      <c r="QE100" s="25"/>
-      <c r="QF100" s="25"/>
-      <c r="QG100" s="25"/>
-      <c r="QH100" s="25"/>
-      <c r="QI100" s="25"/>
-      <c r="QJ100" s="25"/>
-      <c r="QK100" s="25"/>
-      <c r="QL100" s="25"/>
-      <c r="QM100" s="25"/>
-      <c r="QN100" s="25"/>
-      <c r="QO100" s="25"/>
-      <c r="QP100" s="25"/>
-      <c r="QQ100" s="25"/>
-      <c r="QR100" s="25"/>
-      <c r="QS100" s="25"/>
-      <c r="QT100" s="25"/>
-      <c r="QU100" s="25"/>
-      <c r="QV100" s="25"/>
-      <c r="QW100" s="25"/>
-      <c r="QX100" s="25"/>
-      <c r="QY100" s="25"/>
-      <c r="QZ100" s="25"/>
-      <c r="RA100" s="25"/>
-      <c r="RB100" s="25"/>
-      <c r="RC100" s="25"/>
-      <c r="RD100" s="25"/>
-      <c r="RE100" s="25"/>
-      <c r="RF100" s="25"/>
-      <c r="RG100" s="25"/>
-      <c r="RH100" s="25"/>
-      <c r="RI100" s="25"/>
-      <c r="RJ100" s="25"/>
-      <c r="RK100" s="25"/>
-      <c r="RL100" s="25"/>
-      <c r="RM100" s="25"/>
-      <c r="RN100" s="25"/>
-      <c r="RO100" s="25"/>
-      <c r="RP100" s="25"/>
-      <c r="RQ100" s="25"/>
-      <c r="RR100" s="25"/>
-      <c r="RS100" s="25"/>
-      <c r="RT100" s="25"/>
-      <c r="RU100" s="25"/>
-      <c r="RV100" s="25"/>
-      <c r="RW100" s="25"/>
-      <c r="RX100" s="25"/>
-      <c r="RY100" s="25"/>
-      <c r="RZ100" s="25"/>
-      <c r="SA100" s="25"/>
-      <c r="SB100" s="25"/>
-      <c r="SC100" s="25"/>
-      <c r="SD100" s="25"/>
-      <c r="SE100" s="25"/>
-      <c r="SF100" s="25"/>
-      <c r="SG100" s="25"/>
-      <c r="SH100" s="25"/>
-      <c r="SI100" s="25"/>
-      <c r="SJ100" s="25"/>
-      <c r="SK100" s="25"/>
-      <c r="SL100" s="25"/>
-      <c r="SM100" s="25"/>
-      <c r="SN100" s="25"/>
-      <c r="SO100" s="25"/>
-      <c r="SP100" s="25"/>
-      <c r="SQ100" s="25"/>
-      <c r="SR100" s="25"/>
-      <c r="SS100" s="25"/>
-      <c r="ST100" s="25"/>
-      <c r="SU100" s="25"/>
-      <c r="SV100" s="25"/>
-      <c r="SW100" s="25"/>
-      <c r="SX100" s="25"/>
-      <c r="SY100" s="25"/>
-      <c r="SZ100" s="25"/>
-      <c r="TA100" s="25"/>
-      <c r="TB100" s="25"/>
-      <c r="TC100" s="25"/>
-      <c r="TD100" s="25"/>
-      <c r="TE100" s="25"/>
-      <c r="TF100" s="25"/>
-      <c r="TG100" s="25"/>
-      <c r="TH100" s="25"/>
-      <c r="TI100" s="25"/>
-      <c r="TJ100" s="25"/>
-      <c r="TK100" s="25"/>
-      <c r="TL100" s="25"/>
-      <c r="TM100" s="25"/>
-      <c r="TN100" s="25"/>
-      <c r="TO100" s="25"/>
-      <c r="TP100" s="25"/>
-      <c r="TQ100" s="25"/>
-      <c r="TR100" s="25"/>
-      <c r="TS100" s="25"/>
-      <c r="TT100" s="25"/>
-      <c r="TU100" s="25"/>
-      <c r="TV100" s="25"/>
-      <c r="TW100" s="25"/>
-      <c r="TX100" s="25"/>
-      <c r="TY100" s="25"/>
-      <c r="TZ100" s="25"/>
-      <c r="UA100" s="25"/>
-      <c r="UB100" s="25"/>
-      <c r="UC100" s="25"/>
-      <c r="UD100" s="25"/>
-      <c r="UE100" s="25"/>
-      <c r="UF100" s="25"/>
-      <c r="UG100" s="25"/>
-      <c r="UH100" s="25"/>
-      <c r="UI100" s="25"/>
-      <c r="UJ100" s="25"/>
-      <c r="UK100" s="25"/>
-      <c r="UL100" s="25"/>
-      <c r="UM100" s="25"/>
-      <c r="UN100" s="25"/>
-      <c r="UO100" s="25"/>
-      <c r="UP100" s="25"/>
-      <c r="UQ100" s="25"/>
-      <c r="UR100" s="25"/>
-      <c r="US100" s="25"/>
-      <c r="UT100" s="25"/>
-      <c r="UU100" s="25"/>
-      <c r="UV100" s="25"/>
-      <c r="UW100" s="25"/>
-      <c r="UX100" s="25"/>
-      <c r="UY100" s="25"/>
-      <c r="UZ100" s="25"/>
-      <c r="VA100" s="25"/>
-      <c r="VB100" s="25"/>
-      <c r="VC100" s="25"/>
-      <c r="VD100" s="25"/>
-      <c r="VE100" s="25"/>
-      <c r="VF100" s="25"/>
-      <c r="VG100" s="25"/>
-      <c r="VH100" s="25"/>
-      <c r="VI100" s="25"/>
-      <c r="VJ100" s="25"/>
-      <c r="VK100" s="25"/>
-      <c r="VL100" s="25"/>
-      <c r="VM100" s="25"/>
-      <c r="VN100" s="25"/>
-      <c r="VO100" s="25"/>
-      <c r="VP100" s="25"/>
-      <c r="VQ100" s="25"/>
-      <c r="VR100" s="25"/>
-      <c r="VS100" s="25"/>
-      <c r="VT100" s="25"/>
-      <c r="VU100" s="25"/>
-      <c r="VV100" s="25"/>
-      <c r="VW100" s="25"/>
-      <c r="VX100" s="25"/>
-      <c r="VY100" s="25"/>
-      <c r="VZ100" s="25"/>
-      <c r="WA100" s="25"/>
-      <c r="WB100" s="25"/>
-      <c r="WC100" s="25"/>
-      <c r="WD100" s="25"/>
-      <c r="WE100" s="25"/>
-      <c r="WF100" s="25"/>
-      <c r="WG100" s="25"/>
-      <c r="WH100" s="25"/>
-      <c r="WI100" s="25"/>
-      <c r="WJ100" s="25"/>
-      <c r="WK100" s="25"/>
-      <c r="WL100" s="25"/>
-      <c r="WM100" s="25"/>
-      <c r="WN100" s="25"/>
-      <c r="WO100" s="25"/>
-      <c r="WP100" s="25"/>
-      <c r="WQ100" s="25"/>
-      <c r="WR100" s="25"/>
-      <c r="WS100" s="25"/>
-      <c r="WT100" s="25"/>
-      <c r="WU100" s="25"/>
-      <c r="WV100" s="25"/>
-      <c r="WW100" s="25"/>
-      <c r="WX100" s="25"/>
-      <c r="WY100" s="25"/>
-      <c r="WZ100" s="25"/>
-      <c r="XA100" s="25"/>
-      <c r="XB100" s="25"/>
-      <c r="XC100" s="25"/>
-      <c r="XD100" s="25"/>
-      <c r="XE100" s="25"/>
-      <c r="XF100" s="25"/>
-      <c r="XG100" s="25"/>
-      <c r="XH100" s="25"/>
-      <c r="XI100" s="25"/>
-      <c r="XJ100" s="25"/>
-      <c r="XK100" s="25"/>
-      <c r="XL100" s="25"/>
-      <c r="XM100" s="25"/>
-      <c r="XN100" s="25"/>
-      <c r="XO100" s="25"/>
-      <c r="XP100" s="25"/>
-      <c r="XQ100" s="25"/>
-      <c r="XR100" s="25"/>
-      <c r="XS100" s="25"/>
-      <c r="XT100" s="25"/>
-      <c r="XU100" s="25"/>
-      <c r="XV100" s="25"/>
-      <c r="XW100" s="25"/>
-      <c r="XX100" s="25"/>
-      <c r="XY100" s="25"/>
-      <c r="XZ100" s="25"/>
-      <c r="YA100" s="25"/>
-      <c r="YB100" s="25"/>
-      <c r="YC100" s="25"/>
-      <c r="YD100" s="25"/>
-      <c r="YE100" s="25"/>
-      <c r="YF100" s="25"/>
-      <c r="YG100" s="25"/>
-      <c r="YH100" s="25"/>
-      <c r="YI100" s="25"/>
-      <c r="YJ100" s="25"/>
-      <c r="YK100" s="25"/>
-      <c r="YL100" s="25"/>
-      <c r="YM100" s="25"/>
-      <c r="YN100" s="25"/>
-      <c r="YO100" s="25"/>
-      <c r="YP100" s="25"/>
-      <c r="YQ100" s="25"/>
-      <c r="YR100" s="25"/>
-      <c r="YS100" s="25"/>
-      <c r="YT100" s="25"/>
-      <c r="YU100" s="25"/>
-      <c r="YV100" s="25"/>
-      <c r="YW100" s="25"/>
-      <c r="YX100" s="25"/>
-      <c r="YY100" s="25"/>
-      <c r="YZ100" s="25"/>
-      <c r="ZA100" s="25"/>
-      <c r="ZB100" s="25"/>
-      <c r="ZC100" s="25"/>
-      <c r="ZD100" s="25"/>
-      <c r="ZE100" s="25"/>
-      <c r="ZF100" s="25"/>
-      <c r="ZG100" s="25"/>
-      <c r="ZH100" s="25"/>
-      <c r="ZI100" s="25"/>
-      <c r="ZJ100" s="25"/>
-      <c r="ZK100" s="25"/>
-      <c r="ZL100" s="25"/>
-      <c r="ZM100" s="25"/>
-      <c r="ZN100" s="25"/>
-      <c r="ZO100" s="25"/>
-      <c r="ZP100" s="25"/>
-      <c r="ZQ100" s="25"/>
-      <c r="ZR100" s="25"/>
-      <c r="ZS100" s="25"/>
-      <c r="ZT100" s="25"/>
-      <c r="ZU100" s="25"/>
-      <c r="ZV100" s="25"/>
-      <c r="ZW100" s="25"/>
-      <c r="ZX100" s="25"/>
-      <c r="ZY100" s="25"/>
-      <c r="ZZ100" s="25"/>
-      <c r="AAA100" s="25"/>
-      <c r="AAB100" s="25"/>
-      <c r="AAC100" s="25"/>
-      <c r="AAD100" s="25"/>
-      <c r="AAE100" s="25"/>
-      <c r="AAF100" s="25"/>
-      <c r="AAG100" s="25"/>
-      <c r="AAH100" s="25"/>
-      <c r="AAI100" s="25"/>
-      <c r="AAJ100" s="25"/>
-      <c r="AAK100" s="25"/>
-      <c r="AAL100" s="25"/>
-      <c r="AAM100" s="25"/>
-      <c r="AAN100" s="25"/>
-      <c r="AAO100" s="25"/>
-      <c r="AAP100" s="25"/>
-      <c r="AAQ100" s="25"/>
-      <c r="AAR100" s="25"/>
-      <c r="AAS100" s="25"/>
-      <c r="AAT100" s="25"/>
-      <c r="AAU100" s="25"/>
-      <c r="AAV100" s="25"/>
-      <c r="AAW100" s="25"/>
-      <c r="AAX100" s="25"/>
-      <c r="AAY100" s="25"/>
-      <c r="AAZ100" s="25"/>
-      <c r="ABA100" s="25"/>
-      <c r="ABB100" s="25"/>
-      <c r="ABC100" s="25"/>
-      <c r="ABD100" s="25"/>
-      <c r="ABE100" s="25"/>
-      <c r="ABF100" s="25"/>
-      <c r="ABG100" s="25"/>
-      <c r="ABH100" s="25"/>
-      <c r="ABI100" s="25"/>
-      <c r="ABJ100" s="25"/>
-      <c r="ABK100" s="25"/>
-      <c r="ABL100" s="25"/>
-      <c r="ABM100" s="25"/>
-      <c r="ABN100" s="25"/>
-      <c r="ABO100" s="25"/>
-      <c r="ABP100" s="25"/>
-      <c r="ABQ100" s="25"/>
-      <c r="ABR100" s="25"/>
-      <c r="ABS100" s="25"/>
-      <c r="ABT100" s="25"/>
-      <c r="ABU100" s="25"/>
-      <c r="ABV100" s="25"/>
-      <c r="ABW100" s="25"/>
-      <c r="ABX100" s="25"/>
-      <c r="ABY100" s="25"/>
-      <c r="ABZ100" s="25"/>
-      <c r="ACA100" s="25"/>
-      <c r="ACB100" s="25"/>
-      <c r="ACC100" s="25"/>
-      <c r="ACD100" s="25"/>
-      <c r="ACE100" s="25"/>
-      <c r="ACF100" s="25"/>
-      <c r="ACG100" s="25"/>
-      <c r="ACH100" s="25"/>
-      <c r="ACI100" s="25"/>
-      <c r="ACJ100" s="25"/>
-      <c r="ACK100" s="25"/>
-      <c r="ACL100" s="25"/>
-      <c r="ACM100" s="25"/>
-      <c r="ACN100" s="25"/>
-      <c r="ACO100" s="25"/>
-      <c r="ACP100" s="25"/>
-      <c r="ACQ100" s="25"/>
-      <c r="ACR100" s="25"/>
-      <c r="ACS100" s="25"/>
-      <c r="ACT100" s="25"/>
-      <c r="ACU100" s="25"/>
-      <c r="ACV100" s="25"/>
-      <c r="ACW100" s="25"/>
-      <c r="ACX100" s="25"/>
-      <c r="ACY100" s="25"/>
-      <c r="ACZ100" s="25"/>
-      <c r="ADA100" s="25"/>
-      <c r="ADB100" s="25"/>
-      <c r="ADC100" s="25"/>
-      <c r="ADD100" s="25"/>
-      <c r="ADE100" s="25"/>
-      <c r="ADF100" s="25"/>
-      <c r="ADG100" s="25"/>
-      <c r="ADH100" s="25"/>
-      <c r="ADI100" s="25"/>
-      <c r="ADJ100" s="25"/>
-      <c r="ADK100" s="25"/>
-      <c r="ADL100" s="25"/>
-      <c r="ADM100" s="25"/>
-      <c r="ADN100" s="25"/>
-      <c r="ADO100" s="25"/>
-      <c r="ADP100" s="25"/>
-      <c r="ADQ100" s="25"/>
-      <c r="ADR100" s="25"/>
-      <c r="ADS100" s="25"/>
-      <c r="ADT100" s="25"/>
-      <c r="ADU100" s="25"/>
-      <c r="ADV100" s="25"/>
-      <c r="ADW100" s="25"/>
-      <c r="ADX100" s="25"/>
-      <c r="ADY100" s="25"/>
-      <c r="ADZ100" s="25"/>
-      <c r="AEA100" s="25"/>
-      <c r="AEB100" s="25"/>
-      <c r="AEC100" s="25"/>
-      <c r="AED100" s="25"/>
-      <c r="AEE100" s="25"/>
-      <c r="AEF100" s="25"/>
-      <c r="AEG100" s="25"/>
-      <c r="AEH100" s="25"/>
-      <c r="AEI100" s="25"/>
-      <c r="AEJ100" s="25"/>
-      <c r="AEK100" s="25"/>
-      <c r="AEL100" s="25"/>
-      <c r="AEM100" s="25"/>
-      <c r="AEN100" s="25"/>
-      <c r="AEO100" s="25"/>
-      <c r="AEP100" s="25"/>
-      <c r="AEQ100" s="25"/>
-      <c r="AER100" s="25"/>
-      <c r="AES100" s="25"/>
-      <c r="AET100" s="25"/>
-      <c r="AEU100" s="25"/>
-      <c r="AEV100" s="25"/>
-      <c r="AEW100" s="25"/>
-      <c r="AEX100" s="25"/>
-      <c r="AEY100" s="25"/>
-      <c r="AEZ100" s="25"/>
-      <c r="AFA100" s="25"/>
-      <c r="AFB100" s="25"/>
-      <c r="AFC100" s="25"/>
-      <c r="AFD100" s="25"/>
-      <c r="AFE100" s="25"/>
-      <c r="AFF100" s="25"/>
-      <c r="AFG100" s="25"/>
-      <c r="AFH100" s="25"/>
-      <c r="AFI100" s="25"/>
-      <c r="AFJ100" s="25"/>
-      <c r="AFK100" s="25"/>
-      <c r="AFL100" s="25"/>
-      <c r="AFM100" s="25"/>
-      <c r="AFN100" s="25"/>
-      <c r="AFO100" s="25"/>
-      <c r="AFP100" s="25"/>
-      <c r="AFQ100" s="25"/>
-      <c r="AFR100" s="25"/>
-      <c r="AFS100" s="25"/>
-      <c r="AFT100" s="25"/>
-      <c r="AFU100" s="25"/>
-      <c r="AFV100" s="25"/>
-      <c r="AFW100" s="25"/>
-      <c r="AFX100" s="25"/>
-      <c r="AFY100" s="25"/>
-      <c r="AFZ100" s="25"/>
-      <c r="AGA100" s="25"/>
-      <c r="AGB100" s="25"/>
-      <c r="AGC100" s="25"/>
-      <c r="AGD100" s="25"/>
-      <c r="AGE100" s="25"/>
-      <c r="AGF100" s="25"/>
-      <c r="AGG100" s="25"/>
-      <c r="AGH100" s="25"/>
-      <c r="AGI100" s="25"/>
-      <c r="AGJ100" s="25"/>
-      <c r="AGK100" s="25"/>
-      <c r="AGL100" s="25"/>
-      <c r="AGM100" s="25"/>
-      <c r="AGN100" s="25"/>
-      <c r="AGO100" s="25"/>
-      <c r="AGP100" s="25"/>
-      <c r="AGQ100" s="25"/>
-      <c r="AGR100" s="25"/>
-      <c r="AGS100" s="25"/>
-      <c r="AGT100" s="25"/>
-      <c r="AGU100" s="25"/>
-      <c r="AGV100" s="25"/>
-      <c r="AGW100" s="25"/>
-      <c r="AGX100" s="25"/>
-      <c r="AGY100" s="25"/>
-      <c r="AGZ100" s="25"/>
-      <c r="AHA100" s="25"/>
-      <c r="AHB100" s="25"/>
-      <c r="AHC100" s="25"/>
-      <c r="AHD100" s="25"/>
-      <c r="AHE100" s="25"/>
-      <c r="AHF100" s="25"/>
-      <c r="AHG100" s="25"/>
-      <c r="AHH100" s="25"/>
-      <c r="AHI100" s="25"/>
-      <c r="AHJ100" s="25"/>
-      <c r="AHK100" s="25"/>
-      <c r="AHL100" s="25"/>
-      <c r="AHM100" s="25"/>
-      <c r="AHN100" s="25"/>
-      <c r="AHO100" s="25"/>
-      <c r="AHP100" s="25"/>
-      <c r="AHQ100" s="25"/>
-      <c r="AHR100" s="25"/>
-      <c r="AHS100" s="25"/>
-      <c r="AHT100" s="25"/>
-      <c r="AHU100" s="25"/>
-      <c r="AHV100" s="25"/>
-      <c r="AHW100" s="25"/>
-      <c r="AHX100" s="25"/>
-      <c r="AHY100" s="25"/>
-      <c r="AHZ100" s="25"/>
-      <c r="AIA100" s="25"/>
-      <c r="AIB100" s="25"/>
-      <c r="AIC100" s="25"/>
-      <c r="AID100" s="25"/>
-      <c r="AIE100" s="25"/>
-      <c r="AIF100" s="25"/>
-      <c r="AIG100" s="25"/>
-      <c r="AIH100" s="25"/>
-      <c r="AII100" s="25"/>
-      <c r="AIJ100" s="25"/>
-      <c r="AIK100" s="25"/>
-      <c r="AIL100" s="25"/>
-      <c r="AIM100" s="25"/>
-      <c r="AIN100" s="25"/>
-      <c r="AIO100" s="25"/>
-      <c r="AIP100" s="25"/>
-      <c r="AIQ100" s="25"/>
-      <c r="AIR100" s="25"/>
-      <c r="AIS100" s="25"/>
-      <c r="AIT100" s="25"/>
-      <c r="AIU100" s="25"/>
-      <c r="AIV100" s="25"/>
-      <c r="AIW100" s="25"/>
-      <c r="AIX100" s="25"/>
-      <c r="AIY100" s="25"/>
-      <c r="AIZ100" s="25"/>
-      <c r="AJA100" s="25"/>
-      <c r="AJB100" s="25"/>
-      <c r="AJC100" s="25"/>
-      <c r="AJD100" s="25"/>
-      <c r="AJE100" s="25"/>
-      <c r="AJF100" s="25"/>
-      <c r="AJG100" s="25"/>
-      <c r="AJH100" s="25"/>
-      <c r="AJI100" s="25"/>
-      <c r="AJJ100" s="25"/>
-      <c r="AJK100" s="25"/>
-      <c r="AJL100" s="25"/>
-      <c r="AJM100" s="25"/>
-      <c r="AJN100" s="25"/>
-      <c r="AJO100" s="25"/>
-      <c r="AJP100" s="25"/>
-      <c r="AJQ100" s="25"/>
-      <c r="AJR100" s="25"/>
-      <c r="AJS100" s="25"/>
-      <c r="AJT100" s="25"/>
-      <c r="AJU100" s="25"/>
-      <c r="AJV100" s="25"/>
-      <c r="AJW100" s="25"/>
-      <c r="AJX100" s="25"/>
-      <c r="AJY100" s="25"/>
-      <c r="AJZ100" s="25"/>
-      <c r="AKA100" s="25"/>
-      <c r="AKB100" s="25"/>
-      <c r="AKC100" s="25"/>
-      <c r="AKD100" s="25"/>
-      <c r="AKE100" s="25"/>
-      <c r="AKF100" s="25"/>
-      <c r="AKG100" s="25"/>
-      <c r="AKH100" s="25"/>
-      <c r="AKI100" s="25"/>
-      <c r="AKJ100" s="25"/>
-      <c r="AKK100" s="25"/>
-      <c r="AKL100" s="25"/>
-      <c r="AKM100" s="25"/>
-      <c r="AKN100" s="25"/>
-      <c r="AKO100" s="25"/>
-      <c r="AKP100" s="25"/>
-      <c r="AKQ100" s="25"/>
-      <c r="AKR100" s="25"/>
-      <c r="AKS100" s="25"/>
-      <c r="AKT100" s="25"/>
-      <c r="AKU100" s="25"/>
-      <c r="AKV100" s="25"/>
-      <c r="AKW100" s="25"/>
-      <c r="AKX100" s="25"/>
-      <c r="AKY100" s="25"/>
-      <c r="AKZ100" s="25"/>
-      <c r="ALA100" s="25"/>
-      <c r="ALB100" s="25"/>
-      <c r="ALC100" s="25"/>
-      <c r="ALD100" s="25"/>
-      <c r="ALE100" s="25"/>
-      <c r="ALF100" s="25"/>
-      <c r="ALG100" s="25"/>
-      <c r="ALH100" s="25"/>
-      <c r="ALI100" s="25"/>
-      <c r="ALJ100" s="25"/>
-      <c r="ALK100" s="25"/>
-      <c r="ALL100" s="25"/>
-      <c r="ALM100" s="25"/>
-      <c r="ALN100" s="25"/>
-      <c r="ALO100" s="25"/>
-      <c r="ALP100" s="25"/>
-      <c r="ALQ100" s="25"/>
-      <c r="ALR100" s="25"/>
-      <c r="ALS100" s="25"/>
-      <c r="ALT100" s="25"/>
-      <c r="ALU100" s="25"/>
-      <c r="ALV100" s="25"/>
-      <c r="ALW100" s="25"/>
-      <c r="ALX100" s="25"/>
-      <c r="ALY100" s="25"/>
-      <c r="ALZ100" s="25"/>
-      <c r="AMA100" s="25"/>
-      <c r="AMB100" s="25"/>
-      <c r="AMC100" s="25"/>
-      <c r="AMD100" s="25"/>
-      <c r="AME100" s="25"/>
-      <c r="AMF100" s="25"/>
-      <c r="AMG100" s="25"/>
-      <c r="AMH100" s="25"/>
-      <c r="AMI100" s="25"/>
-      <c r="AMJ100" s="25"/>
-      <c r="AMK100" s="25"/>
-      <c r="AML100" s="25"/>
-      <c r="AMM100" s="25"/>
+      <c r="P100" s="12"/>
+      <c r="Q100" s="12"/>
+      <c r="R100" s="12"/>
+      <c r="S100" s="12"/>
+      <c r="T100" s="12"/>
+      <c r="U100" s="12"/>
+      <c r="V100" s="12"/>
+      <c r="W100" s="12"/>
+      <c r="X100" s="12"/>
+      <c r="Y100" s="12"/>
+      <c r="Z100" s="12"/>
+      <c r="AA100" s="12"/>
+      <c r="AB100" s="12"/>
+      <c r="AC100" s="12"/>
+      <c r="AD100" s="12"/>
+      <c r="AE100" s="12"/>
+      <c r="AF100" s="12"/>
+      <c r="AG100" s="12"/>
+      <c r="AH100" s="12"/>
+      <c r="AI100" s="12"/>
+      <c r="AJ100" s="12"/>
+      <c r="AK100" s="12"/>
+      <c r="AL100" s="12"/>
+      <c r="AM100" s="12"/>
+      <c r="AN100" s="12"/>
+      <c r="AO100" s="12"/>
+      <c r="AP100" s="12"/>
+      <c r="AQ100" s="12"/>
+      <c r="AR100" s="12"/>
+      <c r="AS100" s="12"/>
+      <c r="AT100" s="12"/>
+      <c r="AU100" s="12"/>
+      <c r="AV100" s="12"/>
+      <c r="AW100" s="12"/>
+      <c r="AX100" s="12"/>
+      <c r="AY100" s="12"/>
+      <c r="AZ100" s="12"/>
+      <c r="BA100" s="12"/>
+      <c r="BB100" s="12"/>
+      <c r="BC100" s="12"/>
+      <c r="BD100" s="12"/>
+      <c r="BE100" s="12"/>
+      <c r="BF100" s="12"/>
+      <c r="BG100" s="12"/>
+      <c r="BH100" s="12"/>
+      <c r="BI100" s="12"/>
+      <c r="BJ100" s="12"/>
+      <c r="BK100" s="12"/>
+      <c r="BL100" s="12"/>
+      <c r="BM100" s="12"/>
+      <c r="BN100" s="12"/>
+      <c r="BO100" s="12"/>
+      <c r="BP100" s="12"/>
+      <c r="BQ100" s="12"/>
+      <c r="BR100" s="12"/>
+      <c r="BS100" s="12"/>
+      <c r="BT100" s="12"/>
+      <c r="BU100" s="12"/>
+      <c r="BV100" s="12"/>
+      <c r="BW100" s="12"/>
+      <c r="BX100" s="12"/>
+      <c r="BY100" s="12"/>
+      <c r="BZ100" s="12"/>
+      <c r="CA100" s="12"/>
+      <c r="CB100" s="12"/>
+      <c r="CC100" s="12"/>
+      <c r="CD100" s="12"/>
+      <c r="CE100" s="12"/>
+      <c r="CF100" s="12"/>
+      <c r="CG100" s="12"/>
+      <c r="CH100" s="12"/>
+      <c r="CI100" s="12"/>
+      <c r="CJ100" s="12"/>
+      <c r="CK100" s="12"/>
+      <c r="CL100" s="12"/>
+      <c r="CM100" s="12"/>
+      <c r="CN100" s="12"/>
+      <c r="CO100" s="12"/>
+      <c r="CP100" s="12"/>
+      <c r="CQ100" s="12"/>
+      <c r="CR100" s="12"/>
+      <c r="CS100" s="12"/>
+      <c r="CT100" s="12"/>
+      <c r="CU100" s="12"/>
+      <c r="CV100" s="12"/>
+      <c r="CW100" s="12"/>
+      <c r="CX100" s="12"/>
+      <c r="CY100" s="12"/>
+      <c r="CZ100" s="12"/>
+      <c r="DA100" s="12"/>
+      <c r="DB100" s="12"/>
+      <c r="DC100" s="12"/>
+      <c r="DD100" s="12"/>
+      <c r="DE100" s="12"/>
+      <c r="DF100" s="12"/>
+      <c r="DG100" s="12"/>
+      <c r="DH100" s="12"/>
+      <c r="DI100" s="12"/>
+      <c r="DJ100" s="12"/>
+      <c r="DK100" s="12"/>
+      <c r="DL100" s="12"/>
+      <c r="DM100" s="12"/>
+      <c r="DN100" s="12"/>
+      <c r="DO100" s="12"/>
+      <c r="DP100" s="12"/>
+      <c r="DQ100" s="12"/>
+      <c r="DR100" s="12"/>
+      <c r="DS100" s="12"/>
+      <c r="DT100" s="12"/>
+      <c r="DU100" s="12"/>
+      <c r="DV100" s="12"/>
+      <c r="DW100" s="12"/>
+      <c r="DX100" s="12"/>
+      <c r="DY100" s="12"/>
+      <c r="DZ100" s="12"/>
+      <c r="EA100" s="12"/>
+      <c r="EB100" s="12"/>
+      <c r="EC100" s="12"/>
+      <c r="ED100" s="12"/>
+      <c r="EE100" s="12"/>
+      <c r="EF100" s="12"/>
+      <c r="EG100" s="12"/>
+      <c r="EH100" s="12"/>
+      <c r="EI100" s="12"/>
+      <c r="EJ100" s="12"/>
+      <c r="EK100" s="12"/>
+      <c r="EL100" s="12"/>
+      <c r="EM100" s="12"/>
+      <c r="EN100" s="12"/>
+      <c r="EO100" s="12"/>
+      <c r="EP100" s="12"/>
+      <c r="EQ100" s="12"/>
+      <c r="ER100" s="12"/>
+      <c r="ES100" s="12"/>
+      <c r="ET100" s="12"/>
+      <c r="EU100" s="12"/>
+      <c r="EV100" s="12"/>
+      <c r="EW100" s="12"/>
+      <c r="EX100" s="12"/>
+      <c r="EY100" s="12"/>
+      <c r="EZ100" s="12"/>
+      <c r="FA100" s="12"/>
+      <c r="FB100" s="12"/>
+      <c r="FC100" s="12"/>
+      <c r="FD100" s="12"/>
+      <c r="FE100" s="12"/>
+      <c r="FF100" s="12"/>
+      <c r="FG100" s="12"/>
+      <c r="FH100" s="12"/>
+      <c r="FI100" s="12"/>
+      <c r="FJ100" s="12"/>
+      <c r="FK100" s="12"/>
+      <c r="FL100" s="12"/>
+      <c r="FM100" s="12"/>
+      <c r="FN100" s="12"/>
+      <c r="FO100" s="12"/>
+      <c r="FP100" s="12"/>
+      <c r="FQ100" s="12"/>
+      <c r="FR100" s="12"/>
+      <c r="FS100" s="12"/>
+      <c r="FT100" s="12"/>
+      <c r="FU100" s="12"/>
+      <c r="FV100" s="12"/>
+      <c r="FW100" s="12"/>
+      <c r="FX100" s="12"/>
+      <c r="FY100" s="12"/>
+      <c r="FZ100" s="12"/>
+      <c r="GA100" s="12"/>
+      <c r="GB100" s="12"/>
+      <c r="GC100" s="12"/>
+      <c r="GD100" s="12"/>
+      <c r="GE100" s="12"/>
+      <c r="GF100" s="12"/>
+      <c r="GG100" s="12"/>
+      <c r="GH100" s="12"/>
+      <c r="GI100" s="12"/>
+      <c r="GJ100" s="12"/>
+      <c r="GK100" s="12"/>
+      <c r="GL100" s="12"/>
+      <c r="GM100" s="12"/>
+      <c r="GN100" s="12"/>
+      <c r="GO100" s="12"/>
+      <c r="GP100" s="12"/>
+      <c r="GQ100" s="12"/>
+      <c r="GR100" s="12"/>
+      <c r="GS100" s="12"/>
+      <c r="GT100" s="12"/>
+      <c r="GU100" s="12"/>
+      <c r="GV100" s="12"/>
+      <c r="GW100" s="12"/>
+      <c r="GX100" s="12"/>
+      <c r="GY100" s="12"/>
+      <c r="GZ100" s="12"/>
+      <c r="HA100" s="12"/>
+      <c r="HB100" s="12"/>
+      <c r="HC100" s="12"/>
+      <c r="HD100" s="12"/>
+      <c r="HE100" s="12"/>
+      <c r="HF100" s="12"/>
+      <c r="HG100" s="12"/>
+      <c r="HH100" s="12"/>
+      <c r="HI100" s="12"/>
+      <c r="HJ100" s="12"/>
+      <c r="HK100" s="12"/>
+      <c r="HL100" s="12"/>
+      <c r="HM100" s="12"/>
+      <c r="HN100" s="12"/>
+      <c r="HO100" s="12"/>
+      <c r="HP100" s="12"/>
+      <c r="HQ100" s="12"/>
+      <c r="HR100" s="12"/>
+      <c r="HS100" s="12"/>
+      <c r="HT100" s="12"/>
+      <c r="HU100" s="12"/>
+      <c r="HV100" s="12"/>
+      <c r="HW100" s="12"/>
+      <c r="HX100" s="12"/>
+      <c r="HY100" s="12"/>
+      <c r="HZ100" s="12"/>
+      <c r="IA100" s="12"/>
+      <c r="IB100" s="12"/>
+      <c r="IC100" s="12"/>
+      <c r="ID100" s="12"/>
+      <c r="IE100" s="12"/>
+      <c r="IF100" s="12"/>
+      <c r="IG100" s="12"/>
+      <c r="IH100" s="12"/>
+      <c r="II100" s="12"/>
+      <c r="IJ100" s="12"/>
+      <c r="IK100" s="12"/>
+      <c r="IL100" s="12"/>
+      <c r="IM100" s="12"/>
+      <c r="IN100" s="12"/>
+      <c r="IO100" s="12"/>
+      <c r="IP100" s="12"/>
+      <c r="IQ100" s="12"/>
+      <c r="IR100" s="12"/>
+      <c r="IS100" s="12"/>
+      <c r="IT100" s="12"/>
+      <c r="IU100" s="12"/>
+      <c r="IV100" s="12"/>
+      <c r="IW100" s="12"/>
+      <c r="IX100" s="12"/>
+      <c r="IY100" s="12"/>
+      <c r="IZ100" s="12"/>
+      <c r="JA100" s="12"/>
+      <c r="JB100" s="12"/>
+      <c r="JC100" s="12"/>
+      <c r="JD100" s="12"/>
+      <c r="JE100" s="12"/>
+      <c r="JF100" s="12"/>
+      <c r="JG100" s="12"/>
+      <c r="JH100" s="12"/>
+      <c r="JI100" s="12"/>
+      <c r="JJ100" s="12"/>
+      <c r="JK100" s="12"/>
+      <c r="JL100" s="12"/>
+      <c r="JM100" s="12"/>
+      <c r="JN100" s="12"/>
+      <c r="JO100" s="12"/>
+      <c r="JP100" s="12"/>
+      <c r="JQ100" s="12"/>
+      <c r="JR100" s="12"/>
+      <c r="JS100" s="12"/>
+      <c r="JT100" s="12"/>
+      <c r="JU100" s="12"/>
+      <c r="JV100" s="12"/>
+      <c r="JW100" s="12"/>
+      <c r="JX100" s="12"/>
+      <c r="JY100" s="12"/>
+      <c r="JZ100" s="12"/>
+      <c r="KA100" s="12"/>
+      <c r="KB100" s="12"/>
+      <c r="KC100" s="12"/>
+      <c r="KD100" s="12"/>
+      <c r="KE100" s="12"/>
+      <c r="KF100" s="12"/>
+      <c r="KG100" s="12"/>
+      <c r="KH100" s="12"/>
+      <c r="KI100" s="12"/>
+      <c r="KJ100" s="12"/>
+      <c r="KK100" s="12"/>
+      <c r="KL100" s="12"/>
+      <c r="KM100" s="12"/>
+      <c r="KN100" s="12"/>
+      <c r="KO100" s="12"/>
+      <c r="KP100" s="12"/>
+      <c r="KQ100" s="12"/>
+      <c r="KR100" s="12"/>
+      <c r="KS100" s="12"/>
+      <c r="KT100" s="12"/>
+      <c r="KU100" s="12"/>
+      <c r="KV100" s="12"/>
+      <c r="KW100" s="12"/>
+      <c r="KX100" s="12"/>
+      <c r="KY100" s="12"/>
+      <c r="KZ100" s="12"/>
+      <c r="LA100" s="12"/>
+      <c r="LB100" s="12"/>
+      <c r="LC100" s="12"/>
+      <c r="LD100" s="12"/>
+      <c r="LE100" s="12"/>
+      <c r="LF100" s="12"/>
+      <c r="LG100" s="12"/>
+      <c r="LH100" s="12"/>
+      <c r="LI100" s="12"/>
+      <c r="LJ100" s="12"/>
+      <c r="LK100" s="12"/>
+      <c r="LL100" s="12"/>
+      <c r="LM100" s="12"/>
+      <c r="LN100" s="12"/>
+      <c r="LO100" s="12"/>
+      <c r="LP100" s="12"/>
+      <c r="LQ100" s="12"/>
+      <c r="LR100" s="12"/>
+      <c r="LS100" s="12"/>
+      <c r="LT100" s="12"/>
+      <c r="LU100" s="12"/>
+      <c r="LV100" s="12"/>
+      <c r="LW100" s="12"/>
+      <c r="LX100" s="12"/>
+      <c r="LY100" s="12"/>
+      <c r="LZ100" s="12"/>
+      <c r="MA100" s="12"/>
+      <c r="MB100" s="12"/>
+      <c r="MC100" s="12"/>
+      <c r="MD100" s="12"/>
+      <c r="ME100" s="12"/>
+      <c r="MF100" s="12"/>
+      <c r="MG100" s="12"/>
+      <c r="MH100" s="12"/>
+      <c r="MI100" s="12"/>
+      <c r="MJ100" s="12"/>
+      <c r="MK100" s="12"/>
+      <c r="ML100" s="12"/>
+      <c r="MM100" s="12"/>
+      <c r="MN100" s="12"/>
+      <c r="MO100" s="12"/>
+      <c r="MP100" s="12"/>
+      <c r="MQ100" s="12"/>
+      <c r="MR100" s="12"/>
+      <c r="MS100" s="12"/>
+      <c r="MT100" s="12"/>
+      <c r="MU100" s="12"/>
+      <c r="MV100" s="12"/>
+      <c r="MW100" s="12"/>
+      <c r="MX100" s="12"/>
+      <c r="MY100" s="12"/>
+      <c r="MZ100" s="12"/>
+      <c r="NA100" s="12"/>
+      <c r="NB100" s="12"/>
+      <c r="NC100" s="12"/>
+      <c r="ND100" s="12"/>
+      <c r="NE100" s="12"/>
+      <c r="NF100" s="12"/>
+      <c r="NG100" s="12"/>
+      <c r="NH100" s="12"/>
+      <c r="NI100" s="12"/>
+      <c r="NJ100" s="12"/>
+      <c r="NK100" s="12"/>
+      <c r="NL100" s="12"/>
+      <c r="NM100" s="12"/>
+      <c r="NN100" s="12"/>
+      <c r="NO100" s="12"/>
+      <c r="NP100" s="12"/>
+      <c r="NQ100" s="12"/>
+      <c r="NR100" s="12"/>
+      <c r="NS100" s="12"/>
+      <c r="NT100" s="12"/>
+      <c r="NU100" s="12"/>
+      <c r="NV100" s="12"/>
+      <c r="NW100" s="12"/>
+      <c r="NX100" s="12"/>
+      <c r="NY100" s="12"/>
+      <c r="NZ100" s="12"/>
+      <c r="OA100" s="12"/>
+      <c r="OB100" s="12"/>
+      <c r="OC100" s="12"/>
+      <c r="OD100" s="12"/>
+      <c r="OE100" s="12"/>
+      <c r="OF100" s="12"/>
+      <c r="OG100" s="12"/>
+      <c r="OH100" s="12"/>
+      <c r="OI100" s="12"/>
+      <c r="OJ100" s="12"/>
+      <c r="OK100" s="12"/>
+      <c r="OL100" s="12"/>
+      <c r="OM100" s="12"/>
+      <c r="ON100" s="12"/>
+      <c r="OO100" s="12"/>
+      <c r="OP100" s="12"/>
+      <c r="OQ100" s="12"/>
+      <c r="OR100" s="12"/>
+      <c r="OS100" s="12"/>
+      <c r="OT100" s="12"/>
+      <c r="OU100" s="12"/>
+      <c r="OV100" s="12"/>
+      <c r="OW100" s="12"/>
+      <c r="OX100" s="12"/>
+      <c r="OY100" s="12"/>
+      <c r="OZ100" s="12"/>
+      <c r="PA100" s="12"/>
+      <c r="PB100" s="12"/>
+      <c r="PC100" s="12"/>
+      <c r="PD100" s="12"/>
+      <c r="PE100" s="12"/>
+      <c r="PF100" s="12"/>
+      <c r="PG100" s="12"/>
+      <c r="PH100" s="12"/>
+      <c r="PI100" s="12"/>
+      <c r="PJ100" s="12"/>
+      <c r="PK100" s="12"/>
+      <c r="PL100" s="12"/>
+      <c r="PM100" s="12"/>
+      <c r="PN100" s="12"/>
+      <c r="PO100" s="12"/>
+      <c r="PP100" s="12"/>
+      <c r="PQ100" s="12"/>
+      <c r="PR100" s="12"/>
+      <c r="PS100" s="12"/>
+      <c r="PT100" s="12"/>
+      <c r="PU100" s="12"/>
+      <c r="PV100" s="12"/>
+      <c r="PW100" s="12"/>
+      <c r="PX100" s="12"/>
+      <c r="PY100" s="12"/>
+      <c r="PZ100" s="12"/>
+      <c r="QA100" s="12"/>
+      <c r="QB100" s="12"/>
+      <c r="QC100" s="12"/>
+      <c r="QD100" s="12"/>
+      <c r="QE100" s="12"/>
+      <c r="QF100" s="12"/>
+      <c r="QG100" s="12"/>
+      <c r="QH100" s="12"/>
+      <c r="QI100" s="12"/>
+      <c r="QJ100" s="12"/>
+      <c r="QK100" s="12"/>
+      <c r="QL100" s="12"/>
+      <c r="QM100" s="12"/>
+      <c r="QN100" s="12"/>
+      <c r="QO100" s="12"/>
+      <c r="QP100" s="12"/>
+      <c r="QQ100" s="12"/>
+      <c r="QR100" s="12"/>
+      <c r="QS100" s="12"/>
+      <c r="QT100" s="12"/>
+      <c r="QU100" s="12"/>
+      <c r="QV100" s="12"/>
+      <c r="QW100" s="12"/>
+      <c r="QX100" s="12"/>
+      <c r="QY100" s="12"/>
+      <c r="QZ100" s="12"/>
+      <c r="RA100" s="12"/>
+      <c r="RB100" s="12"/>
+      <c r="RC100" s="12"/>
+      <c r="RD100" s="12"/>
+      <c r="RE100" s="12"/>
+      <c r="RF100" s="12"/>
+      <c r="RG100" s="12"/>
+      <c r="RH100" s="12"/>
+      <c r="RI100" s="12"/>
+      <c r="RJ100" s="12"/>
+      <c r="RK100" s="12"/>
+      <c r="RL100" s="12"/>
+      <c r="RM100" s="12"/>
+      <c r="RN100" s="12"/>
+      <c r="RO100" s="12"/>
+      <c r="RP100" s="12"/>
+      <c r="RQ100" s="12"/>
+      <c r="RR100" s="12"/>
+      <c r="RS100" s="12"/>
+      <c r="RT100" s="12"/>
+      <c r="RU100" s="12"/>
+      <c r="RV100" s="12"/>
+      <c r="RW100" s="12"/>
+      <c r="RX100" s="12"/>
+      <c r="RY100" s="12"/>
+      <c r="RZ100" s="12"/>
+      <c r="SA100" s="12"/>
+      <c r="SB100" s="12"/>
+      <c r="SC100" s="12"/>
+      <c r="SD100" s="12"/>
+      <c r="SE100" s="12"/>
+      <c r="SF100" s="12"/>
+      <c r="SG100" s="12"/>
+      <c r="SH100" s="12"/>
+      <c r="SI100" s="12"/>
+      <c r="SJ100" s="12"/>
+      <c r="SK100" s="12"/>
+      <c r="SL100" s="12"/>
+      <c r="SM100" s="12"/>
+      <c r="SN100" s="12"/>
+      <c r="SO100" s="12"/>
+      <c r="SP100" s="12"/>
+      <c r="SQ100" s="12"/>
+      <c r="SR100" s="12"/>
+      <c r="SS100" s="12"/>
+      <c r="ST100" s="12"/>
+      <c r="SU100" s="12"/>
+      <c r="SV100" s="12"/>
+      <c r="SW100" s="12"/>
+      <c r="SX100" s="12"/>
+      <c r="SY100" s="12"/>
+      <c r="SZ100" s="12"/>
+      <c r="TA100" s="12"/>
+      <c r="TB100" s="12"/>
+      <c r="TC100" s="12"/>
+      <c r="TD100" s="12"/>
+      <c r="TE100" s="12"/>
+      <c r="TF100" s="12"/>
+      <c r="TG100" s="12"/>
+      <c r="TH100" s="12"/>
+      <c r="TI100" s="12"/>
+      <c r="TJ100" s="12"/>
+      <c r="TK100" s="12"/>
+      <c r="TL100" s="12"/>
+      <c r="TM100" s="12"/>
+      <c r="TN100" s="12"/>
+      <c r="TO100" s="12"/>
+      <c r="TP100" s="12"/>
+      <c r="TQ100" s="12"/>
+      <c r="TR100" s="12"/>
+      <c r="TS100" s="12"/>
+      <c r="TT100" s="12"/>
+      <c r="TU100" s="12"/>
+      <c r="TV100" s="12"/>
+      <c r="TW100" s="12"/>
+      <c r="TX100" s="12"/>
+      <c r="TY100" s="12"/>
+      <c r="TZ100" s="12"/>
+      <c r="UA100" s="12"/>
+      <c r="UB100" s="12"/>
+      <c r="UC100" s="12"/>
+      <c r="UD100" s="12"/>
+      <c r="UE100" s="12"/>
+      <c r="UF100" s="12"/>
+      <c r="UG100" s="12"/>
+      <c r="UH100" s="12"/>
+      <c r="UI100" s="12"/>
+      <c r="UJ100" s="12"/>
+      <c r="UK100" s="12"/>
+      <c r="UL100" s="12"/>
+      <c r="UM100" s="12"/>
+      <c r="UN100" s="12"/>
+      <c r="UO100" s="12"/>
+      <c r="UP100" s="12"/>
+      <c r="UQ100" s="12"/>
+      <c r="UR100" s="12"/>
+      <c r="US100" s="12"/>
+      <c r="UT100" s="12"/>
+      <c r="UU100" s="12"/>
+      <c r="UV100" s="12"/>
+      <c r="UW100" s="12"/>
+      <c r="UX100" s="12"/>
+      <c r="UY100" s="12"/>
+      <c r="UZ100" s="12"/>
+      <c r="VA100" s="12"/>
+      <c r="VB100" s="12"/>
+      <c r="VC100" s="12"/>
+      <c r="VD100" s="12"/>
+      <c r="VE100" s="12"/>
+      <c r="VF100" s="12"/>
+      <c r="VG100" s="12"/>
+      <c r="VH100" s="12"/>
+      <c r="VI100" s="12"/>
+      <c r="VJ100" s="12"/>
+      <c r="VK100" s="12"/>
+      <c r="VL100" s="12"/>
+      <c r="VM100" s="12"/>
+      <c r="VN100" s="12"/>
+      <c r="VO100" s="12"/>
+      <c r="VP100" s="12"/>
+      <c r="VQ100" s="12"/>
+      <c r="VR100" s="12"/>
+      <c r="VS100" s="12"/>
+      <c r="VT100" s="12"/>
+      <c r="VU100" s="12"/>
+      <c r="VV100" s="12"/>
+      <c r="VW100" s="12"/>
+      <c r="VX100" s="12"/>
+      <c r="VY100" s="12"/>
+      <c r="VZ100" s="12"/>
+      <c r="WA100" s="12"/>
+      <c r="WB100" s="12"/>
+      <c r="WC100" s="12"/>
+      <c r="WD100" s="12"/>
+      <c r="WE100" s="12"/>
+      <c r="WF100" s="12"/>
+      <c r="WG100" s="12"/>
+      <c r="WH100" s="12"/>
+      <c r="WI100" s="12"/>
+      <c r="WJ100" s="12"/>
+      <c r="WK100" s="12"/>
+      <c r="WL100" s="12"/>
+      <c r="WM100" s="12"/>
+      <c r="WN100" s="12"/>
+      <c r="WO100" s="12"/>
+      <c r="WP100" s="12"/>
+      <c r="WQ100" s="12"/>
+      <c r="WR100" s="12"/>
+      <c r="WS100" s="12"/>
+      <c r="WT100" s="12"/>
+      <c r="WU100" s="12"/>
+      <c r="WV100" s="12"/>
+      <c r="WW100" s="12"/>
+      <c r="WX100" s="12"/>
+      <c r="WY100" s="12"/>
+      <c r="WZ100" s="12"/>
+      <c r="XA100" s="12"/>
+      <c r="XB100" s="12"/>
+      <c r="XC100" s="12"/>
+      <c r="XD100" s="12"/>
+      <c r="XE100" s="12"/>
+      <c r="XF100" s="12"/>
+      <c r="XG100" s="12"/>
+      <c r="XH100" s="12"/>
+      <c r="XI100" s="12"/>
+      <c r="XJ100" s="12"/>
+      <c r="XK100" s="12"/>
+      <c r="XL100" s="12"/>
+      <c r="XM100" s="12"/>
+      <c r="XN100" s="12"/>
+      <c r="XO100" s="12"/>
+      <c r="XP100" s="12"/>
+      <c r="XQ100" s="12"/>
+      <c r="XR100" s="12"/>
+      <c r="XS100" s="12"/>
+      <c r="XT100" s="12"/>
+      <c r="XU100" s="12"/>
+      <c r="XV100" s="12"/>
+      <c r="XW100" s="12"/>
+      <c r="XX100" s="12"/>
+      <c r="XY100" s="12"/>
+      <c r="XZ100" s="12"/>
+      <c r="YA100" s="12"/>
+      <c r="YB100" s="12"/>
+      <c r="YC100" s="12"/>
+      <c r="YD100" s="12"/>
+      <c r="YE100" s="12"/>
+      <c r="YF100" s="12"/>
+      <c r="YG100" s="12"/>
+      <c r="YH100" s="12"/>
+      <c r="YI100" s="12"/>
+      <c r="YJ100" s="12"/>
+      <c r="YK100" s="12"/>
+      <c r="YL100" s="12"/>
+      <c r="YM100" s="12"/>
+      <c r="YN100" s="12"/>
+      <c r="YO100" s="12"/>
+      <c r="YP100" s="12"/>
+      <c r="YQ100" s="12"/>
+      <c r="YR100" s="12"/>
+      <c r="YS100" s="12"/>
+      <c r="YT100" s="12"/>
+      <c r="YU100" s="12"/>
+      <c r="YV100" s="12"/>
+      <c r="YW100" s="12"/>
+      <c r="YX100" s="12"/>
+      <c r="YY100" s="12"/>
+      <c r="YZ100" s="12"/>
+      <c r="ZA100" s="12"/>
+      <c r="ZB100" s="12"/>
+      <c r="ZC100" s="12"/>
+      <c r="ZD100" s="12"/>
+      <c r="ZE100" s="12"/>
+      <c r="ZF100" s="12"/>
+      <c r="ZG100" s="12"/>
+      <c r="ZH100" s="12"/>
+      <c r="ZI100" s="12"/>
+      <c r="ZJ100" s="12"/>
+      <c r="ZK100" s="12"/>
+      <c r="ZL100" s="12"/>
+      <c r="ZM100" s="12"/>
+      <c r="ZN100" s="12"/>
+      <c r="ZO100" s="12"/>
+      <c r="ZP100" s="12"/>
+      <c r="ZQ100" s="12"/>
+      <c r="ZR100" s="12"/>
+      <c r="ZS100" s="12"/>
+      <c r="ZT100" s="12"/>
+      <c r="ZU100" s="12"/>
+      <c r="ZV100" s="12"/>
+      <c r="ZW100" s="12"/>
+      <c r="ZX100" s="12"/>
+      <c r="ZY100" s="12"/>
+      <c r="ZZ100" s="12"/>
+      <c r="AAA100" s="12"/>
+      <c r="AAB100" s="12"/>
+      <c r="AAC100" s="12"/>
+      <c r="AAD100" s="12"/>
+      <c r="AAE100" s="12"/>
+      <c r="AAF100" s="12"/>
+      <c r="AAG100" s="12"/>
+      <c r="AAH100" s="12"/>
+      <c r="AAI100" s="12"/>
+      <c r="AAJ100" s="12"/>
+      <c r="AAK100" s="12"/>
+      <c r="AAL100" s="12"/>
+      <c r="AAM100" s="12"/>
+      <c r="AAN100" s="12"/>
+      <c r="AAO100" s="12"/>
+      <c r="AAP100" s="12"/>
+      <c r="AAQ100" s="12"/>
+      <c r="AAR100" s="12"/>
+      <c r="AAS100" s="12"/>
+      <c r="AAT100" s="12"/>
+      <c r="AAU100" s="12"/>
+      <c r="AAV100" s="12"/>
+      <c r="AAW100" s="12"/>
+      <c r="AAX100" s="12"/>
+      <c r="AAY100" s="12"/>
+      <c r="AAZ100" s="12"/>
+      <c r="ABA100" s="12"/>
+      <c r="ABB100" s="12"/>
+      <c r="ABC100" s="12"/>
+      <c r="ABD100" s="12"/>
+      <c r="ABE100" s="12"/>
+      <c r="ABF100" s="12"/>
+      <c r="ABG100" s="12"/>
+      <c r="ABH100" s="12"/>
+      <c r="ABI100" s="12"/>
+      <c r="ABJ100" s="12"/>
+      <c r="ABK100" s="12"/>
+      <c r="ABL100" s="12"/>
+      <c r="ABM100" s="12"/>
+      <c r="ABN100" s="12"/>
+      <c r="ABO100" s="12"/>
+      <c r="ABP100" s="12"/>
+      <c r="ABQ100" s="12"/>
+      <c r="ABR100" s="12"/>
+      <c r="ABS100" s="12"/>
+      <c r="ABT100" s="12"/>
+      <c r="ABU100" s="12"/>
+      <c r="ABV100" s="12"/>
+      <c r="ABW100" s="12"/>
+      <c r="ABX100" s="12"/>
+      <c r="ABY100" s="12"/>
+      <c r="ABZ100" s="12"/>
+      <c r="ACA100" s="12"/>
+      <c r="ACB100" s="12"/>
+      <c r="ACC100" s="12"/>
+      <c r="ACD100" s="12"/>
+      <c r="ACE100" s="12"/>
+      <c r="ACF100" s="12"/>
+      <c r="ACG100" s="12"/>
+      <c r="ACH100" s="12"/>
+      <c r="ACI100" s="12"/>
+      <c r="ACJ100" s="12"/>
+      <c r="ACK100" s="12"/>
+      <c r="ACL100" s="12"/>
+      <c r="ACM100" s="12"/>
+      <c r="ACN100" s="12"/>
+      <c r="ACO100" s="12"/>
+      <c r="ACP100" s="12"/>
+      <c r="ACQ100" s="12"/>
+      <c r="ACR100" s="12"/>
+      <c r="ACS100" s="12"/>
+      <c r="ACT100" s="12"/>
+      <c r="ACU100" s="12"/>
+      <c r="ACV100" s="12"/>
+      <c r="ACW100" s="12"/>
+      <c r="ACX100" s="12"/>
+      <c r="ACY100" s="12"/>
+      <c r="ACZ100" s="12"/>
+      <c r="ADA100" s="12"/>
+      <c r="ADB100" s="12"/>
+      <c r="ADC100" s="12"/>
+      <c r="ADD100" s="12"/>
+      <c r="ADE100" s="12"/>
+      <c r="ADF100" s="12"/>
+      <c r="ADG100" s="12"/>
+      <c r="ADH100" s="12"/>
+      <c r="ADI100" s="12"/>
+      <c r="ADJ100" s="12"/>
+      <c r="ADK100" s="12"/>
+      <c r="ADL100" s="12"/>
+      <c r="ADM100" s="12"/>
+      <c r="ADN100" s="12"/>
+      <c r="ADO100" s="12"/>
+      <c r="ADP100" s="12"/>
+      <c r="ADQ100" s="12"/>
+      <c r="ADR100" s="12"/>
+      <c r="ADS100" s="12"/>
+      <c r="ADT100" s="12"/>
+      <c r="ADU100" s="12"/>
+      <c r="ADV100" s="12"/>
+      <c r="ADW100" s="12"/>
+      <c r="ADX100" s="12"/>
+      <c r="ADY100" s="12"/>
+      <c r="ADZ100" s="12"/>
+      <c r="AEA100" s="12"/>
+      <c r="AEB100" s="12"/>
+      <c r="AEC100" s="12"/>
+      <c r="AED100" s="12"/>
+      <c r="AEE100" s="12"/>
+      <c r="AEF100" s="12"/>
+      <c r="AEG100" s="12"/>
+      <c r="AEH100" s="12"/>
+      <c r="AEI100" s="12"/>
+      <c r="AEJ100" s="12"/>
+      <c r="AEK100" s="12"/>
+      <c r="AEL100" s="12"/>
+      <c r="AEM100" s="12"/>
+      <c r="AEN100" s="12"/>
+      <c r="AEO100" s="12"/>
+      <c r="AEP100" s="12"/>
+      <c r="AEQ100" s="12"/>
+      <c r="AER100" s="12"/>
+      <c r="AES100" s="12"/>
+      <c r="AET100" s="12"/>
+      <c r="AEU100" s="12"/>
+      <c r="AEV100" s="12"/>
+      <c r="AEW100" s="12"/>
+      <c r="AEX100" s="12"/>
+      <c r="AEY100" s="12"/>
+      <c r="AEZ100" s="12"/>
+      <c r="AFA100" s="12"/>
+      <c r="AFB100" s="12"/>
+      <c r="AFC100" s="12"/>
+      <c r="AFD100" s="12"/>
+      <c r="AFE100" s="12"/>
+      <c r="AFF100" s="12"/>
+      <c r="AFG100" s="12"/>
+      <c r="AFH100" s="12"/>
+      <c r="AFI100" s="12"/>
+      <c r="AFJ100" s="12"/>
+      <c r="AFK100" s="12"/>
+      <c r="AFL100" s="12"/>
+      <c r="AFM100" s="12"/>
+      <c r="AFN100" s="12"/>
+      <c r="AFO100" s="12"/>
+      <c r="AFP100" s="12"/>
+      <c r="AFQ100" s="12"/>
+      <c r="AFR100" s="12"/>
+      <c r="AFS100" s="12"/>
+      <c r="AFT100" s="12"/>
+      <c r="AFU100" s="12"/>
+      <c r="AFV100" s="12"/>
+      <c r="AFW100" s="12"/>
+      <c r="AFX100" s="12"/>
+      <c r="AFY100" s="12"/>
+      <c r="AFZ100" s="12"/>
+      <c r="AGA100" s="12"/>
+      <c r="AGB100" s="12"/>
+      <c r="AGC100" s="12"/>
+      <c r="AGD100" s="12"/>
+      <c r="AGE100" s="12"/>
+      <c r="AGF100" s="12"/>
+      <c r="AGG100" s="12"/>
+      <c r="AGH100" s="12"/>
+      <c r="AGI100" s="12"/>
+      <c r="AGJ100" s="12"/>
+      <c r="AGK100" s="12"/>
+      <c r="AGL100" s="12"/>
+      <c r="AGM100" s="12"/>
+      <c r="AGN100" s="12"/>
+      <c r="AGO100" s="12"/>
+      <c r="AGP100" s="12"/>
+      <c r="AGQ100" s="12"/>
+      <c r="AGR100" s="12"/>
+      <c r="AGS100" s="12"/>
+      <c r="AGT100" s="12"/>
+      <c r="AGU100" s="12"/>
+      <c r="AGV100" s="12"/>
+      <c r="AGW100" s="12"/>
+      <c r="AGX100" s="12"/>
+      <c r="AGY100" s="12"/>
+      <c r="AGZ100" s="12"/>
+      <c r="AHA100" s="12"/>
+      <c r="AHB100" s="12"/>
+      <c r="AHC100" s="12"/>
+      <c r="AHD100" s="12"/>
+      <c r="AHE100" s="12"/>
+      <c r="AHF100" s="12"/>
+      <c r="AHG100" s="12"/>
+      <c r="AHH100" s="12"/>
+      <c r="AHI100" s="12"/>
+      <c r="AHJ100" s="12"/>
+      <c r="AHK100" s="12"/>
+      <c r="AHL100" s="12"/>
+      <c r="AHM100" s="12"/>
+      <c r="AHN100" s="12"/>
+      <c r="AHO100" s="12"/>
+      <c r="AHP100" s="12"/>
+      <c r="AHQ100" s="12"/>
+      <c r="AHR100" s="12"/>
+      <c r="AHS100" s="12"/>
+      <c r="AHT100" s="12"/>
+      <c r="AHU100" s="12"/>
+      <c r="AHV100" s="12"/>
+      <c r="AHW100" s="12"/>
+      <c r="AHX100" s="12"/>
+      <c r="AHY100" s="12"/>
+      <c r="AHZ100" s="12"/>
+      <c r="AIA100" s="12"/>
+      <c r="AIB100" s="12"/>
+      <c r="AIC100" s="12"/>
+      <c r="AID100" s="12"/>
+      <c r="AIE100" s="12"/>
+      <c r="AIF100" s="12"/>
+      <c r="AIG100" s="12"/>
+      <c r="AIH100" s="12"/>
+      <c r="AII100" s="12"/>
+      <c r="AIJ100" s="12"/>
+      <c r="AIK100" s="12"/>
+      <c r="AIL100" s="12"/>
+      <c r="AIM100" s="12"/>
+      <c r="AIN100" s="12"/>
+      <c r="AIO100" s="12"/>
+      <c r="AIP100" s="12"/>
+      <c r="AIQ100" s="12"/>
+      <c r="AIR100" s="12"/>
+      <c r="AIS100" s="12"/>
+      <c r="AIT100" s="12"/>
+      <c r="AIU100" s="12"/>
+      <c r="AIV100" s="12"/>
+      <c r="AIW100" s="12"/>
+      <c r="AIX100" s="12"/>
+      <c r="AIY100" s="12"/>
+      <c r="AIZ100" s="12"/>
+      <c r="AJA100" s="12"/>
+      <c r="AJB100" s="12"/>
+      <c r="AJC100" s="12"/>
+      <c r="AJD100" s="12"/>
+      <c r="AJE100" s="12"/>
+      <c r="AJF100" s="12"/>
+      <c r="AJG100" s="12"/>
+      <c r="AJH100" s="12"/>
+      <c r="AJI100" s="12"/>
+      <c r="AJJ100" s="12"/>
+      <c r="AJK100" s="12"/>
+      <c r="AJL100" s="12"/>
+      <c r="AJM100" s="12"/>
+      <c r="AJN100" s="12"/>
+      <c r="AJO100" s="12"/>
+      <c r="AJP100" s="12"/>
+      <c r="AJQ100" s="12"/>
+      <c r="AJR100" s="12"/>
+      <c r="AJS100" s="12"/>
+      <c r="AJT100" s="12"/>
+      <c r="AJU100" s="12"/>
+      <c r="AJV100" s="12"/>
+      <c r="AJW100" s="12"/>
+      <c r="AJX100" s="12"/>
+      <c r="AJY100" s="12"/>
+      <c r="AJZ100" s="12"/>
+      <c r="AKA100" s="12"/>
+      <c r="AKB100" s="12"/>
+      <c r="AKC100" s="12"/>
+      <c r="AKD100" s="12"/>
+      <c r="AKE100" s="12"/>
+      <c r="AKF100" s="12"/>
+      <c r="AKG100" s="12"/>
+      <c r="AKH100" s="12"/>
+      <c r="AKI100" s="12"/>
+      <c r="AKJ100" s="12"/>
+      <c r="AKK100" s="12"/>
+      <c r="AKL100" s="12"/>
+      <c r="AKM100" s="12"/>
+      <c r="AKN100" s="12"/>
+      <c r="AKO100" s="12"/>
+      <c r="AKP100" s="12"/>
+      <c r="AKQ100" s="12"/>
+      <c r="AKR100" s="12"/>
+      <c r="AKS100" s="12"/>
+      <c r="AKT100" s="12"/>
+      <c r="AKU100" s="12"/>
+      <c r="AKV100" s="12"/>
+      <c r="AKW100" s="12"/>
+      <c r="AKX100" s="12"/>
+      <c r="AKY100" s="12"/>
+      <c r="AKZ100" s="12"/>
+      <c r="ALA100" s="12"/>
+      <c r="ALB100" s="12"/>
+      <c r="ALC100" s="12"/>
+      <c r="ALD100" s="12"/>
+      <c r="ALE100" s="12"/>
+      <c r="ALF100" s="12"/>
+      <c r="ALG100" s="12"/>
+      <c r="ALH100" s="12"/>
+      <c r="ALI100" s="12"/>
+      <c r="ALJ100" s="12"/>
+      <c r="ALK100" s="12"/>
+      <c r="ALL100" s="12"/>
+      <c r="ALM100" s="12"/>
+      <c r="ALN100" s="12"/>
+      <c r="ALO100" s="12"/>
+      <c r="ALP100" s="12"/>
+      <c r="ALQ100" s="12"/>
+      <c r="ALR100" s="12"/>
+      <c r="ALS100" s="12"/>
+      <c r="ALT100" s="12"/>
+      <c r="ALU100" s="12"/>
+      <c r="ALV100" s="12"/>
+      <c r="ALW100" s="12"/>
+      <c r="ALX100" s="12"/>
+      <c r="ALY100" s="12"/>
+      <c r="ALZ100" s="12"/>
+      <c r="AMA100" s="12"/>
+      <c r="AMB100" s="12"/>
+      <c r="AMC100" s="12"/>
+      <c r="AMD100" s="12"/>
+      <c r="AME100" s="12"/>
+      <c r="AMF100" s="12"/>
+      <c r="AMG100" s="12"/>
+      <c r="AMH100" s="12"/>
+      <c r="AMI100" s="12"/>
+      <c r="AMJ100" s="12"/>
+      <c r="AMK100" s="12"/>
+      <c r="AML100" s="12"/>
+      <c r="AMM100" s="12"/>
     </row>
     <row r="101" spans="1:1027" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">

--- a/work-in-progress/Peppol Code Lists - Participant identifier schemes v9.6.xlsx
+++ b/work-in-progress/Peppol Code Lists - Participant identifier schemes v9.6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\git-peppol\peppol-edec-codelists\work-in-progress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD9742D-9F42-4682-B8C7-6135057DA094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492BB87D-252F-400C-951D-A839BDA32449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="720" windowWidth="25875" windowHeight="20160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22110" yWindow="0" windowWidth="19935" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Participant Identifier Scheme" sheetId="1" r:id="rId1"/>
@@ -2026,7 +2026,215 @@
     <t>UAE Federal Tax Authority</t>
   </si>
   <si>
-    <t>A TIN comprises of 10 numerical digits:
+    <t>[1][23456789][X]: The first digit from the left must always be "1"</t>
+  </si>
+  <si>
+    <t>RegEx: 1[0-9]{9}</t>
+  </si>
+  <si>
+    <t>LU:MAT</t>
+  </si>
+  <si>
+    <t>0240</t>
+  </si>
+  <si>
+    <t>Register of legal persons</t>
+  </si>
+  <si>
+    <t>Centre des technologies de l'information de l'Etat (CTIE)</t>
+  </si>
+  <si>
+    <t>RegEx: [0-9]{11}</t>
+  </si>
+  <si>
+    <t>- 11 characters in total (Arabic numerals only)
+- 4 first digits = year (may be 0000)
+- Digits 5-6 = legal form of the legal person
+Checksum: digit 11</t>
+  </si>
+  <si>
+    <t>SPIS</t>
+  </si>
+  <si>
+    <t>0242</t>
+  </si>
+  <si>
+    <t>OpenPeppol Service Provider Identification Scheme</t>
+  </si>
+  <si>
+    <t>OpenPeppol AISBL</t>
+  </si>
+  <si>
+    <t>9.3</t>
+  </si>
+  <si>
+    <t>The identifier must follow the following regular expression in a
+case-insensitive way:
+[0-9]{6}(-[0-9A-Z_]{3,12}(\.[0-9A-Z\-\._~]{3,24})?)?
+The identifier consists of one to three parts: number of characters
+and their significance, if any
+- The mandatory Main ID - 6 characters
+- The optional Peppol Use Case ID - 3 to 12 characters
+- The optional Service Provider Suffix - 3 to 24 characters</t>
+  </si>
+  <si>
+    <t>Must follow the structure of the identifier</t>
+  </si>
+  <si>
+    <t>RegEx: [0-9]{6}(-[0-9A-Z_]{3,12}(\.[0-9A-Z\-\._~]{3,24})?)?</t>
+  </si>
+  <si>
+    <t>The identifier will have several applications within the Peppol
+Network.</t>
+  </si>
+  <si>
+    <t>Replaced by 0190</t>
+  </si>
+  <si>
+    <t>Get all OIN’s from: https://oinregister.logius.nl/oin-register</t>
+  </si>
+  <si>
+    <t>0244</t>
+  </si>
+  <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>Tax Identification (Tax ID)</t>
+  </si>
+  <si>
+    <t>Federal Inland Revenue Service Revenue (FIRS)</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>Displayed as a 13-digit numeric string (e.g., 0000000000244) without separators.</t>
+  </si>
+  <si>
+    <t>RegEx: [0-9]{13}</t>
+  </si>
+  <si>
+    <t>TINs are mandatory for all activities, tax filings, financial reporting, and government-related transactions in Nigeria</t>
+  </si>
+  <si>
+    <t>NG:TID</t>
+  </si>
+  <si>
+    <t>13 digits for Tax ID assigned to organizations
+- YY - Last two digits of issuance year (e.g., 25 for 2025).
+- SRC -Source of identity: 1 for individuals (NIN-based) 2 for corporate entities (CAC-based).
+- SC - Numeric state code based on national standard (e.g., 24 for Lagos).
+- HashFragment - 7-digit numeric fragment derived from the NIN or CAC Registration Number by extracting only numeric characters from a cryptographic hash (e.g., SHA-256).
+- CheckDigit - Single-digit checksum calculated using the Luhn (Modulus 10) algorithm applied to the preceding numeric portion of the Tax ID.
+Validation is done through internal database cross-checking and NIN/CAC registration linkages</t>
+  </si>
+  <si>
+    <t>SK:DIC</t>
+  </si>
+  <si>
+    <t>0245</t>
+  </si>
+  <si>
+    <t>Tax identification number (DIČ)</t>
+  </si>
+  <si>
+    <t>The tax office according to the local jurisdiction of the taxpayer.
+Head office:
+Financial Directorate of the Slovak Republic
+Lazovná 63 , Banská Bystrica
+974 01 Banská Bystrica
+Slovakia</t>
+  </si>
+  <si>
+    <t>10 characters (fixed length), the first digit determines the type of person or status of the person:
+1- natural person
+2- legal entity
+3- foreign natural person
+4- foreign legal entity
+5- registered organizational unit
+6- tax representative for the import of goods
+7- VAT group
+The DIČ number is divisible by 11.</t>
+  </si>
+  <si>
+    <t>The DIČ number is given as a single 10-digit number.</t>
+  </si>
+  <si>
+    <t>The tax identification number (DIČ) is an identifier that taxpayers are required to provide when dealing with the tax administrator.</t>
+  </si>
+  <si>
+    <t>DE:GEBA</t>
+  </si>
+  <si>
+    <t>0246</t>
+  </si>
+  <si>
+    <t>German Electronic Business Address</t>
+  </si>
+  <si>
+    <t>Koordinierungsstelle für IT-Standards (KoSIT)</t>
+  </si>
+  <si>
+    <t>The identifier must follow the following regular expression in a case-insensitive way:
+DE[0-9]{9}(-[0-9]{5})?(\.[0-9A-Z]{1,8})?
+The identifier consists of one to three parts:
+• The mandatory business identification number (W-IdNr) – DE followed by 9 digits
+• The optional “distinctive feature (“Unterscheidungsmerkmal”) – separated by a hyphen and followed by 5 digits
+• The optional “sub-address” suffix – separated by a period (Full stop) followed by 1 to 8 characters
+The 9th digit of the business identification number (W-IdNr) is a check digit covering the preceding 8 digits.</t>
+  </si>
+  <si>
+    <t>A GEBA is displayed as an alpha-numerical string value of all parts and separators.</t>
+  </si>
+  <si>
+    <t>RegEx: DE[0-9]{9}(-[0-9]{5})?(\.[0-9A-Z]{1,8})?</t>
+  </si>
+  <si>
+    <t>Organizations may only use their assigned business identification number. Organizations publish their GEBA including potential sub-address suffixes themselves</t>
+  </si>
+  <si>
+    <t>OM:VAT</t>
+  </si>
+  <si>
+    <t>0248</t>
+  </si>
+  <si>
+    <t>OM</t>
+  </si>
+  <si>
+    <t>Oman Value Added Tax Identification Number (VATIN)</t>
+  </si>
+  <si>
+    <t>Tax Authority, Oman</t>
+  </si>
+  <si>
+    <t>9.6</t>
+  </si>
+  <si>
+    <t>12 characters including 2 letters and 10 digits numbers e.g., OM1100003554
+[1-2] positions contain country identifier (OM for Oman)
+[3-4] positions represent the location (residence/non-residence) and type of the organization (group/individual)
+[5-12] positions generated automatically by OTA'S Tax Management System (TMS) at the time of registration.</t>
+  </si>
+  <si>
+    <t>12 characters including 2 letters and 10 digits numbers e.g., OM1100003554</t>
+  </si>
+  <si>
+    <t>OM1100003554</t>
+  </si>
+  <si>
+    <t>RegEx: OM[0-9]{10}</t>
+  </si>
+  <si>
+    <t>All organizations that are registered for VAT in Oman are obligated to issue and/or receive invoice electronically in the Sultanate of Oman and shall use the VATIN allocated by the Oman Tax Authority to uniquely identify themselves.</t>
+  </si>
+  <si>
+    <t>Use 0208 instead</t>
+  </si>
+  <si>
+    <t>The Tax Identification Number (TIN) is a unique number issued and managed solely by the UAE Federal Tax Authority (FTA) for each registered taxpayer. It is an official identifier that cannot be created or assigned by any other party.
+A TIN comprises of 10 numerical digits:
 - [1]: UAE country identifier in accordance with GCC agreement. This number must always be "1"
 - [23456789]: business identifier, generated automatically by the FTA's core tax administration system at the time a person presents themselves for registration
 - [X]: check digit (mathematically derived by adopting Luhn's
@@ -2038,213 +2246,6 @@
   c. Take the sum of the digits from step b above
   d. Mod 10 of the unit's place of the sum of the values in
 step c above</t>
-  </si>
-  <si>
-    <t>[1][23456789][X]: The first digit from the left must always be "1"</t>
-  </si>
-  <si>
-    <t>RegEx: 1[0-9]{9}</t>
-  </si>
-  <si>
-    <t>LU:MAT</t>
-  </si>
-  <si>
-    <t>0240</t>
-  </si>
-  <si>
-    <t>Register of legal persons</t>
-  </si>
-  <si>
-    <t>Centre des technologies de l'information de l'Etat (CTIE)</t>
-  </si>
-  <si>
-    <t>RegEx: [0-9]{11}</t>
-  </si>
-  <si>
-    <t>- 11 characters in total (Arabic numerals only)
-- 4 first digits = year (may be 0000)
-- Digits 5-6 = legal form of the legal person
-Checksum: digit 11</t>
-  </si>
-  <si>
-    <t>SPIS</t>
-  </si>
-  <si>
-    <t>0242</t>
-  </si>
-  <si>
-    <t>OpenPeppol Service Provider Identification Scheme</t>
-  </si>
-  <si>
-    <t>OpenPeppol AISBL</t>
-  </si>
-  <si>
-    <t>9.3</t>
-  </si>
-  <si>
-    <t>The identifier must follow the following regular expression in a
-case-insensitive way:
-[0-9]{6}(-[0-9A-Z_]{3,12}(\.[0-9A-Z\-\._~]{3,24})?)?
-The identifier consists of one to three parts: number of characters
-and their significance, if any
-- The mandatory Main ID - 6 characters
-- The optional Peppol Use Case ID - 3 to 12 characters
-- The optional Service Provider Suffix - 3 to 24 characters</t>
-  </si>
-  <si>
-    <t>Must follow the structure of the identifier</t>
-  </si>
-  <si>
-    <t>RegEx: [0-9]{6}(-[0-9A-Z_]{3,12}(\.[0-9A-Z\-\._~]{3,24})?)?</t>
-  </si>
-  <si>
-    <t>The identifier will have several applications within the Peppol
-Network.</t>
-  </si>
-  <si>
-    <t>Replaced by 0190</t>
-  </si>
-  <si>
-    <t>Get all OIN’s from: https://oinregister.logius.nl/oin-register</t>
-  </si>
-  <si>
-    <t>0244</t>
-  </si>
-  <si>
-    <t>NG</t>
-  </si>
-  <si>
-    <t>Tax Identification (Tax ID)</t>
-  </si>
-  <si>
-    <t>Federal Inland Revenue Service Revenue (FIRS)</t>
-  </si>
-  <si>
-    <t>9.5</t>
-  </si>
-  <si>
-    <t>Displayed as a 13-digit numeric string (e.g., 0000000000244) without separators.</t>
-  </si>
-  <si>
-    <t>RegEx: [0-9]{13}</t>
-  </si>
-  <si>
-    <t>TINs are mandatory for all activities, tax filings, financial reporting, and government-related transactions in Nigeria</t>
-  </si>
-  <si>
-    <t>NG:TID</t>
-  </si>
-  <si>
-    <t>13 digits for Tax ID assigned to organizations
-- YY - Last two digits of issuance year (e.g., 25 for 2025).
-- SRC -Source of identity: 1 for individuals (NIN-based) 2 for corporate entities (CAC-based).
-- SC - Numeric state code based on national standard (e.g., 24 for Lagos).
-- HashFragment - 7-digit numeric fragment derived from the NIN or CAC Registration Number by extracting only numeric characters from a cryptographic hash (e.g., SHA-256).
-- CheckDigit - Single-digit checksum calculated using the Luhn (Modulus 10) algorithm applied to the preceding numeric portion of the Tax ID.
-Validation is done through internal database cross-checking and NIN/CAC registration linkages</t>
-  </si>
-  <si>
-    <t>SK:DIC</t>
-  </si>
-  <si>
-    <t>0245</t>
-  </si>
-  <si>
-    <t>Tax identification number (DIČ)</t>
-  </si>
-  <si>
-    <t>The tax office according to the local jurisdiction of the taxpayer.
-Head office:
-Financial Directorate of the Slovak Republic
-Lazovná 63 , Banská Bystrica
-974 01 Banská Bystrica
-Slovakia</t>
-  </si>
-  <si>
-    <t>10 characters (fixed length), the first digit determines the type of person or status of the person:
-1- natural person
-2- legal entity
-3- foreign natural person
-4- foreign legal entity
-5- registered organizational unit
-6- tax representative for the import of goods
-7- VAT group
-The DIČ number is divisible by 11.</t>
-  </si>
-  <si>
-    <t>The DIČ number is given as a single 10-digit number.</t>
-  </si>
-  <si>
-    <t>The tax identification number (DIČ) is an identifier that taxpayers are required to provide when dealing with the tax administrator.</t>
-  </si>
-  <si>
-    <t>DE:GEBA</t>
-  </si>
-  <si>
-    <t>0246</t>
-  </si>
-  <si>
-    <t>German Electronic Business Address</t>
-  </si>
-  <si>
-    <t>Koordinierungsstelle für IT-Standards (KoSIT)</t>
-  </si>
-  <si>
-    <t>The identifier must follow the following regular expression in a case-insensitive way:
-DE[0-9]{9}(-[0-9]{5})?(\.[0-9A-Z]{1,8})?
-The identifier consists of one to three parts:
-• The mandatory business identification number (W-IdNr) – DE followed by 9 digits
-• The optional “distinctive feature (“Unterscheidungsmerkmal”) – separated by a hyphen and followed by 5 digits
-• The optional “sub-address” suffix – separated by a period (Full stop) followed by 1 to 8 characters
-The 9th digit of the business identification number (W-IdNr) is a check digit covering the preceding 8 digits.</t>
-  </si>
-  <si>
-    <t>A GEBA is displayed as an alpha-numerical string value of all parts and separators.</t>
-  </si>
-  <si>
-    <t>RegEx: DE[0-9]{9}(-[0-9]{5})?(\.[0-9A-Z]{1,8})?</t>
-  </si>
-  <si>
-    <t>Organizations may only use their assigned business identification number. Organizations publish their GEBA including potential sub-address suffixes themselves</t>
-  </si>
-  <si>
-    <t>OM:VAT</t>
-  </si>
-  <si>
-    <t>0248</t>
-  </si>
-  <si>
-    <t>OM</t>
-  </si>
-  <si>
-    <t>Oman Value Added Tax Identification Number (VATIN)</t>
-  </si>
-  <si>
-    <t>Tax Authority, Oman</t>
-  </si>
-  <si>
-    <t>9.6</t>
-  </si>
-  <si>
-    <t>12 characters including 2 letters and 10 digits numbers e.g., OM1100003554
-[1-2] positions contain country identifier (OM for Oman)
-[3-4] positions represent the location (residence/non-residence) and type of the organization (group/individual)
-[5-12] positions generated automatically by OTA'S Tax Management System (TMS) at the time of registration.</t>
-  </si>
-  <si>
-    <t>12 characters including 2 letters and 10 digits numbers e.g., OM1100003554</t>
-  </si>
-  <si>
-    <t>OM1100003554</t>
-  </si>
-  <si>
-    <t>RegEx: OM[0-9]{10}</t>
-  </si>
-  <si>
-    <t>All organizations that are registered for VAT in Oman are obligated to issue and/or receive invoice electronically in the Sultanate of Oman and shall use the VATIN allocated by the Oman Tax Authority to uniquely identify themselves.</t>
-  </si>
-  <si>
-    <t>Use 0208 instead</t>
   </si>
 </sst>
 </file>
@@ -4796,7 +4797,7 @@
         <v>430</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="O18" s="7" t="s">
         <v>528</v>
@@ -4904,7 +4905,7 @@
         <v>483</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I21" s="30">
         <v>46210</v>
@@ -4920,7 +4921,7 @@
         <v>433</v>
       </c>
       <c r="N21" s="25" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="O21" s="27" t="s">
         <v>528</v>
@@ -9739,7 +9740,7 @@
       </c>
       <c r="AMN41" s="4"/>
     </row>
-    <row r="42" spans="1:1028" ht="240" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1028" ht="315" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>573</v>
       </c>
@@ -9762,14 +9763,14 @@
         <v>482</v>
       </c>
       <c r="J42" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="K42" s="6" t="s">
         <v>578</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>579</v>
       </c>
       <c r="L42" s="8"/>
       <c r="M42" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O42" s="7" t="s">
         <v>528</v>
@@ -9778,19 +9779,19 @@
     </row>
     <row r="43" spans="1:1028" ht="60" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>581</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>582</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>253</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>583</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>584</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>568</v>
@@ -9799,14 +9800,14 @@
         <v>482</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>32</v>
       </c>
       <c r="L43" s="8"/>
       <c r="M43" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="O43" s="4" t="s">
         <v>528</v>
@@ -9815,38 +9816,38 @@
     </row>
     <row r="44" spans="1:1028" ht="120" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>587</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>588</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D44" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="F44" s="9" t="s">
         <v>590</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>591</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>482</v>
       </c>
       <c r="J44" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="K44" s="6" t="s">
         <v>592</v>
-      </c>
-      <c r="K44" s="6" t="s">
-        <v>593</v>
       </c>
       <c r="L44" s="8"/>
       <c r="M44" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="N44" s="4" t="s">
         <v>594</v>
-      </c>
-      <c r="N44" s="4" t="s">
-        <v>595</v>
       </c>
       <c r="O44" s="4" t="s">
         <v>528</v>
@@ -9855,38 +9856,38 @@
     </row>
     <row r="45" spans="1:1028" ht="180" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="D45" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="F45" s="9" t="s">
         <v>601</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>602</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>482</v>
       </c>
       <c r="J45" s="19" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L45" s="8"/>
       <c r="M45" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="N45" s="4" t="s">
         <v>604</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>605</v>
       </c>
       <c r="O45" s="4" t="s">
         <v>528</v>
@@ -9895,38 +9896,38 @@
     </row>
     <row r="46" spans="1:1028" ht="150" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>608</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>609</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>300</v>
       </c>
       <c r="D46" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>611</v>
-      </c>
       <c r="F46" s="9" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>482</v>
       </c>
       <c r="J46" s="19" t="s">
+        <v>611</v>
+      </c>
+      <c r="K46" s="6" t="s">
         <v>612</v>
-      </c>
-      <c r="K46" s="6" t="s">
-        <v>613</v>
       </c>
       <c r="L46" s="8"/>
       <c r="M46" s="7" t="s">
         <v>555</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="O46" s="4" t="s">
         <v>528</v>
@@ -9935,38 +9936,38 @@
     </row>
     <row r="47" spans="1:1028" ht="180" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>615</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>616</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>223</v>
       </c>
       <c r="D47" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>618</v>
-      </c>
       <c r="F47" s="9" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>482</v>
       </c>
       <c r="J47" s="19" t="s">
+        <v>618</v>
+      </c>
+      <c r="K47" s="6" t="s">
         <v>619</v>
-      </c>
-      <c r="K47" s="6" t="s">
-        <v>620</v>
       </c>
       <c r="L47" s="8"/>
       <c r="M47" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="N47" s="4" t="s">
         <v>621</v>
-      </c>
-      <c r="N47" s="4" t="s">
-        <v>622</v>
       </c>
       <c r="O47" s="4" t="s">
         <v>528</v>
@@ -9975,40 +9976,40 @@
     </row>
     <row r="48" spans="1:1028" ht="150" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="C48" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="D48" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="E48" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="F48" s="9" t="s">
         <v>627</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>628</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>482</v>
       </c>
       <c r="J48" s="19" t="s">
+        <v>628</v>
+      </c>
+      <c r="K48" s="6" t="s">
         <v>629</v>
       </c>
-      <c r="K48" s="6" t="s">
+      <c r="L48" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="L48" s="8" t="s">
+      <c r="M48" s="7" t="s">
         <v>631</v>
       </c>
-      <c r="M48" s="7" t="s">
+      <c r="N48" s="4" t="s">
         <v>632</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>633</v>
       </c>
       <c r="O48" s="4" t="s">
         <v>528</v>
@@ -23644,7 +23645,7 @@
       <c r="L100" s="14"/>
       <c r="M100" s="14"/>
       <c r="N100" s="12" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="O100" s="14" t="s">
         <v>529</v>
